--- a/inasistencias-6A-sistDeCtrolVirtual/Alumnos-6A-SistDeCtrolVirtual.xlsx
+++ b/inasistencias-6A-sistDeCtrolVirtual/Alumnos-6A-SistDeCtrolVirtual.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="282">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -56,6 +56,9 @@
     <t xml:space="preserve">P</t>
   </si>
   <si>
+    <t xml:space="preserve">T</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lourdes Elizabeth</t>
   </si>
   <si>
@@ -83,6 +86,9 @@
     <t xml:space="preserve">aybarguillermo@gmail.com</t>
   </si>
   <si>
+    <t xml:space="preserve">p</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sathya</t>
   </si>
   <si>
@@ -92,6 +98,9 @@
     <t xml:space="preserve">sathyxzz@gmail.com</t>
   </si>
   <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
@@ -128,9 +137,6 @@
     <t xml:space="preserve">liamdifebo15@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
     <t xml:space="preserve">Francisco Gael</t>
   </si>
   <si>
@@ -248,10 +254,13 @@
     <t xml:space="preserve">tarde</t>
   </si>
   <si>
-    <t xml:space="preserve">olimpiadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toal</t>
+    <t xml:space="preserve">total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
   </si>
   <si>
     <t xml:space="preserve">positivos</t>
@@ -804,9 +813,6 @@
   </si>
   <si>
     <t xml:space="preserve">5 minutos 11 segundos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total</t>
   </si>
   <si>
     <t xml:space="preserve">45 minutos 55 segundos</t>
@@ -876,9 +882,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="166" formatCode="hh:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -946,7 +953,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -960,6 +967,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1120,7 +1139,7 @@
         <v>46091</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>46098</v>
+        <v>46140</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>46105</v>
@@ -1261,6 +1280,9 @@
       </c>
       <c r="E3" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1268,15 +1290,18 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1285,15 +1310,18 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1302,16 +1330,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1319,16 +1350,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1336,18 +1370,20 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -1510,15 +1546,18 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1527,15 +1566,18 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1544,16 +1586,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1561,18 +1606,20 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -1735,15 +1782,18 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1752,16 +1802,19 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1769,18 +1822,20 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -1943,15 +1998,18 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1960,15 +2018,18 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1977,18 +2038,20 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="1"/>
+      <c r="F18" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -2151,18 +2214,20 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="1"/>
+      <c r="F19" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -2325,15 +2390,18 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2342,16 +2410,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2359,15 +2430,18 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="WXY22" s="2"/>
@@ -2564,18 +2638,20 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F23" s="1"/>
+      <c r="F23" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -2923,35 +2999,61 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E24" s="1" t="n">
         <f aca="false">COUNTIF(E3:E23,"P")</f>
         <v>20</v>
       </c>
+      <c r="F24" s="1" t="n">
+        <f aca="false">COUNTIF(F3:F23,"P")</f>
+        <v>13</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <f aca="false">COUNTIF(E3:E23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <f aca="false">COUNTIF(F3:F23,"M")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <f aca="false">COUNTIF(E3:E23,"t")</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <f aca="false">COUNTIF(F3:F23,"t")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <f aca="false">SUM(E24:E26)</f>
+        <v>20</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <f aca="false">SUM(F24:F26)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="C28" s="0"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
@@ -2987,19 +3089,19 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3021,16 +3123,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -3044,7 +3146,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -3058,16 +3160,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>8</v>
@@ -3081,7 +3183,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -3095,7 +3197,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -3109,16 +3211,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>6</v>
@@ -3132,16 +3234,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -3160,13 +3262,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9</v>
@@ -3177,16 +3279,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7</v>
@@ -3205,13 +3307,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>6</v>
@@ -3222,7 +3324,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>1</v>
@@ -3236,16 +3338,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -3259,16 +3361,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9</v>
@@ -3282,7 +3384,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -3296,16 +3398,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>6</v>
@@ -3319,7 +3421,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -3333,7 +3435,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>1</v>
@@ -3347,7 +3449,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>1</v>
@@ -3361,7 +3463,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>1</v>
@@ -3375,7 +3477,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>1</v>
@@ -3389,7 +3491,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>1</v>
@@ -3403,16 +3505,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>7</v>
@@ -3431,13 +3533,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>5</v>
@@ -3445,13 +3547,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>5</v>
@@ -3462,7 +3564,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>1</v>
@@ -3473,7 +3575,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G28" s="1" t="s">
-        <v>258</v>
+        <v>74</v>
       </c>
       <c r="I28" s="1" t="n">
         <f aca="false">COUNTIF(I2:I27,"&gt;0")</f>
@@ -3517,10 +3619,10 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3537,7 +3639,7 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>8.5</v>
@@ -3548,16 +3650,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>7</v>
@@ -3568,16 +3670,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -3588,16 +3690,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>9</v>
@@ -3608,7 +3710,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -3619,16 +3721,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -3639,16 +3741,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>8.75</v>
@@ -3659,16 +3761,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -3679,16 +3781,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8.75</v>
@@ -3699,16 +3801,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>8.25</v>
@@ -3719,16 +3821,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8.75</v>
@@ -3739,16 +3841,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9.5</v>
@@ -3759,16 +3861,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>7.25</v>
@@ -3779,16 +3881,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9.25</v>
@@ -3799,16 +3901,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>7.25</v>
@@ -3819,7 +3921,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -3830,16 +3932,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>9</v>
@@ -3850,16 +3952,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8.5</v>
@@ -3870,16 +3972,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8.5</v>
@@ -3890,16 +3992,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -3910,16 +4012,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9.25</v>
@@ -3930,16 +4032,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -3961,13 +4063,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AMM1048576"/>
+  <dimension ref="A1:AMO27"/>
   <sheetFormatPr defaultColWidth="9.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="973" min="973" style="1" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16331" style="0" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="975" min="975" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16333" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3980,1206 +4082,1011 @@
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C2" s="3" t="n">
+        <v>46091</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>46105</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>46112</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>46119</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>46126</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>46133</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>46147</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>46161</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>46175</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>46182</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>46189</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>46196</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>46210</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="AB2" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="AC2" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="AD2" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="AF2" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="AG2" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="AH2" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="AI2" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="AJ2" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="AL2" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="AM2" s="3" t="n">
+        <v>46329</v>
+      </c>
+      <c r="AN2" s="3" t="n">
+        <v>46336</v>
+      </c>
+      <c r="AO2" s="3" t="n">
+        <v>46343</v>
+      </c>
+      <c r="AP2" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="AQ2" s="3" t="n">
+        <v>46357</v>
+      </c>
+      <c r="AR2" s="3" t="n">
+        <v>46364</v>
+      </c>
+      <c r="AS2" s="3" t="n">
+        <v>46371</v>
+      </c>
+      <c r="AT2" s="3" t="n">
+        <v>46378</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="AKL3" s="0"/>
-      <c r="AKM3" s="0"/>
-      <c r="AKN3" s="0"/>
-      <c r="AKO3" s="0"/>
-      <c r="AKP3" s="0"/>
-      <c r="AKQ3" s="0"/>
-      <c r="AKR3" s="0"/>
-      <c r="AKS3" s="0"/>
-      <c r="AKT3" s="0"/>
-      <c r="AKU3" s="0"/>
-      <c r="AKV3" s="0"/>
-      <c r="AKW3" s="0"/>
-      <c r="AKX3" s="0"/>
-      <c r="AKY3" s="0"/>
-      <c r="AKZ3" s="0"/>
-      <c r="ALA3" s="0"/>
-      <c r="ALB3" s="0"/>
-      <c r="ALC3" s="0"/>
-      <c r="ALD3" s="0"/>
-      <c r="ALE3" s="0"/>
-      <c r="ALF3" s="0"/>
-      <c r="ALG3" s="0"/>
-      <c r="ALH3" s="0"/>
-      <c r="ALI3" s="0"/>
-      <c r="ALJ3" s="0"/>
-      <c r="ALK3" s="0"/>
-      <c r="ALL3" s="0"/>
-      <c r="ALM3" s="0"/>
-      <c r="ALN3" s="0"/>
-      <c r="ALO3" s="0"/>
-      <c r="ALP3" s="0"/>
-      <c r="ALQ3" s="0"/>
-      <c r="ALR3" s="0"/>
-      <c r="ALS3" s="0"/>
-      <c r="ALT3" s="0"/>
-      <c r="ALU3" s="0"/>
-      <c r="ALV3" s="0"/>
-      <c r="ALW3" s="0"/>
-      <c r="ALX3" s="0"/>
-      <c r="ALY3" s="0"/>
-      <c r="ALZ3" s="0"/>
-      <c r="AMA3" s="0"/>
-      <c r="AMB3" s="0"/>
-      <c r="AMC3" s="0"/>
-      <c r="AMD3" s="0"/>
-      <c r="AME3" s="0"/>
-      <c r="AMF3" s="0"/>
-      <c r="AMG3" s="0"/>
-      <c r="AMH3" s="0"/>
-      <c r="AMI3" s="0"/>
-      <c r="AMJ3" s="0"/>
-      <c r="AMK3" s="0"/>
-      <c r="AML3" s="0"/>
-      <c r="AMM3" s="0"/>
-    </row>
-    <row r="4" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="AKL4" s="0"/>
-      <c r="AKM4" s="0"/>
-      <c r="AKN4" s="0"/>
-      <c r="AKO4" s="0"/>
-      <c r="AKP4" s="0"/>
-      <c r="AKQ4" s="0"/>
-      <c r="AKR4" s="0"/>
-      <c r="AKS4" s="0"/>
-      <c r="AKT4" s="0"/>
-      <c r="AKU4" s="0"/>
-      <c r="AKV4" s="0"/>
-      <c r="AKW4" s="0"/>
-      <c r="AKX4" s="0"/>
-      <c r="AKY4" s="0"/>
-      <c r="AKZ4" s="0"/>
-      <c r="ALA4" s="0"/>
-      <c r="ALB4" s="0"/>
-      <c r="ALC4" s="0"/>
-      <c r="ALD4" s="0"/>
-      <c r="ALE4" s="0"/>
-      <c r="ALF4" s="0"/>
-      <c r="ALG4" s="0"/>
-      <c r="ALH4" s="0"/>
-      <c r="ALI4" s="0"/>
-      <c r="ALJ4" s="0"/>
-      <c r="ALK4" s="0"/>
-      <c r="ALL4" s="0"/>
-      <c r="ALM4" s="0"/>
-      <c r="ALN4" s="0"/>
-      <c r="ALO4" s="0"/>
-      <c r="ALP4" s="0"/>
-      <c r="ALQ4" s="0"/>
-      <c r="ALR4" s="0"/>
-      <c r="ALS4" s="0"/>
-      <c r="ALT4" s="0"/>
-      <c r="ALU4" s="0"/>
-      <c r="ALV4" s="0"/>
-      <c r="ALW4" s="0"/>
-      <c r="ALX4" s="0"/>
-      <c r="ALY4" s="0"/>
-      <c r="ALZ4" s="0"/>
-      <c r="AMA4" s="0"/>
-      <c r="AMB4" s="0"/>
-      <c r="AMC4" s="0"/>
-      <c r="AMD4" s="0"/>
-      <c r="AME4" s="0"/>
-      <c r="AMF4" s="0"/>
-      <c r="AMG4" s="0"/>
-      <c r="AMH4" s="0"/>
-      <c r="AMI4" s="0"/>
-      <c r="AMJ4" s="0"/>
-      <c r="AMK4" s="0"/>
-      <c r="AML4" s="0"/>
-      <c r="AMM4" s="0"/>
-    </row>
-    <row r="5" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="AKL5" s="0"/>
-      <c r="AKM5" s="0"/>
-      <c r="AKN5" s="0"/>
-      <c r="AKO5" s="0"/>
-      <c r="AKP5" s="0"/>
-      <c r="AKQ5" s="0"/>
-      <c r="AKR5" s="0"/>
-      <c r="AKS5" s="0"/>
-      <c r="AKT5" s="0"/>
-      <c r="AKU5" s="0"/>
-      <c r="AKV5" s="0"/>
-      <c r="AKW5" s="0"/>
-      <c r="AKX5" s="0"/>
-      <c r="AKY5" s="0"/>
-      <c r="AKZ5" s="0"/>
-      <c r="ALA5" s="0"/>
-      <c r="ALB5" s="0"/>
-      <c r="ALC5" s="0"/>
-      <c r="ALD5" s="0"/>
-      <c r="ALE5" s="0"/>
-      <c r="ALF5" s="0"/>
-      <c r="ALG5" s="0"/>
-      <c r="ALH5" s="0"/>
-      <c r="ALI5" s="0"/>
-      <c r="ALJ5" s="0"/>
-      <c r="ALK5" s="0"/>
-      <c r="ALL5" s="0"/>
-      <c r="ALM5" s="0"/>
-      <c r="ALN5" s="0"/>
-      <c r="ALO5" s="0"/>
-      <c r="ALP5" s="0"/>
-      <c r="ALQ5" s="0"/>
-      <c r="ALR5" s="0"/>
-      <c r="ALS5" s="0"/>
-      <c r="ALT5" s="0"/>
-      <c r="ALU5" s="0"/>
-      <c r="ALV5" s="0"/>
-      <c r="ALW5" s="0"/>
-      <c r="ALX5" s="0"/>
-      <c r="ALY5" s="0"/>
-      <c r="ALZ5" s="0"/>
-      <c r="AMA5" s="0"/>
-      <c r="AMB5" s="0"/>
-      <c r="AMC5" s="0"/>
-      <c r="AMD5" s="0"/>
-      <c r="AME5" s="0"/>
-      <c r="AMF5" s="0"/>
-      <c r="AMG5" s="0"/>
-      <c r="AMH5" s="0"/>
-      <c r="AMI5" s="0"/>
-      <c r="AMJ5" s="0"/>
-      <c r="AMK5" s="0"/>
-      <c r="AML5" s="0"/>
-      <c r="AMM5" s="0"/>
-    </row>
-    <row r="6" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AKL6" s="0"/>
-      <c r="AKM6" s="0"/>
-      <c r="AKN6" s="0"/>
-      <c r="AKO6" s="0"/>
-      <c r="AKP6" s="0"/>
-      <c r="AKQ6" s="0"/>
-      <c r="AKR6" s="0"/>
-      <c r="AKS6" s="0"/>
-      <c r="AKT6" s="0"/>
-      <c r="AKU6" s="0"/>
-      <c r="AKV6" s="0"/>
-      <c r="AKW6" s="0"/>
-      <c r="AKX6" s="0"/>
-      <c r="AKY6" s="0"/>
-      <c r="AKZ6" s="0"/>
-      <c r="ALA6" s="0"/>
-      <c r="ALB6" s="0"/>
-      <c r="ALC6" s="0"/>
-      <c r="ALD6" s="0"/>
-      <c r="ALE6" s="0"/>
-      <c r="ALF6" s="0"/>
-      <c r="ALG6" s="0"/>
-      <c r="ALH6" s="0"/>
-      <c r="ALI6" s="0"/>
-      <c r="ALJ6" s="0"/>
-      <c r="ALK6" s="0"/>
-      <c r="ALL6" s="0"/>
-      <c r="ALM6" s="0"/>
-      <c r="ALN6" s="0"/>
-      <c r="ALO6" s="0"/>
-      <c r="ALP6" s="0"/>
-      <c r="ALQ6" s="0"/>
-      <c r="ALR6" s="0"/>
-      <c r="ALS6" s="0"/>
-      <c r="ALT6" s="0"/>
-      <c r="ALU6" s="0"/>
-      <c r="ALV6" s="0"/>
-      <c r="ALW6" s="0"/>
-      <c r="ALX6" s="0"/>
-      <c r="ALY6" s="0"/>
-      <c r="ALZ6" s="0"/>
-      <c r="AMA6" s="0"/>
-      <c r="AMB6" s="0"/>
-      <c r="AMC6" s="0"/>
-      <c r="AMD6" s="0"/>
-      <c r="AME6" s="0"/>
-      <c r="AMF6" s="0"/>
-      <c r="AMG6" s="0"/>
-      <c r="AMH6" s="0"/>
-      <c r="AMI6" s="0"/>
-      <c r="AMJ6" s="0"/>
-      <c r="AMK6" s="0"/>
-      <c r="AML6" s="0"/>
-      <c r="AMM6" s="0"/>
-    </row>
-    <row r="7" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AKL7" s="0"/>
-      <c r="AKM7" s="0"/>
-      <c r="AKN7" s="0"/>
-      <c r="AKO7" s="0"/>
-      <c r="AKP7" s="0"/>
-      <c r="AKQ7" s="0"/>
-      <c r="AKR7" s="0"/>
-      <c r="AKS7" s="0"/>
-      <c r="AKT7" s="0"/>
-      <c r="AKU7" s="0"/>
-      <c r="AKV7" s="0"/>
-      <c r="AKW7" s="0"/>
-      <c r="AKX7" s="0"/>
-      <c r="AKY7" s="0"/>
-      <c r="AKZ7" s="0"/>
-      <c r="ALA7" s="0"/>
-      <c r="ALB7" s="0"/>
-      <c r="ALC7" s="0"/>
-      <c r="ALD7" s="0"/>
-      <c r="ALE7" s="0"/>
-      <c r="ALF7" s="0"/>
-      <c r="ALG7" s="0"/>
-      <c r="ALH7" s="0"/>
-      <c r="ALI7" s="0"/>
-      <c r="ALJ7" s="0"/>
-      <c r="ALK7" s="0"/>
-      <c r="ALL7" s="0"/>
-      <c r="ALM7" s="0"/>
-      <c r="ALN7" s="0"/>
-      <c r="ALO7" s="0"/>
-      <c r="ALP7" s="0"/>
-      <c r="ALQ7" s="0"/>
-      <c r="ALR7" s="0"/>
-      <c r="ALS7" s="0"/>
-      <c r="ALT7" s="0"/>
-      <c r="ALU7" s="0"/>
-      <c r="ALV7" s="0"/>
-      <c r="ALW7" s="0"/>
-      <c r="ALX7" s="0"/>
-      <c r="ALY7" s="0"/>
-      <c r="ALZ7" s="0"/>
-      <c r="AMA7" s="0"/>
-      <c r="AMB7" s="0"/>
-      <c r="AMC7" s="0"/>
-      <c r="AMD7" s="0"/>
-      <c r="AME7" s="0"/>
-      <c r="AMF7" s="0"/>
-      <c r="AMG7" s="0"/>
-      <c r="AMH7" s="0"/>
-      <c r="AMI7" s="0"/>
-      <c r="AMJ7" s="0"/>
-      <c r="AMK7" s="0"/>
-      <c r="AML7" s="0"/>
-      <c r="AMM7" s="0"/>
-    </row>
-    <row r="8" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.534722222222222</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="AKK8" s="1"/>
-      <c r="AKL8" s="0"/>
-      <c r="AKM8" s="0"/>
-      <c r="AKN8" s="0"/>
-      <c r="AKO8" s="0"/>
-      <c r="AKP8" s="0"/>
-      <c r="AKQ8" s="0"/>
-      <c r="AKR8" s="0"/>
-      <c r="AKS8" s="0"/>
-      <c r="AKT8" s="0"/>
-      <c r="AKU8" s="0"/>
-      <c r="AKV8" s="0"/>
-      <c r="AKW8" s="0"/>
-      <c r="AKX8" s="0"/>
-      <c r="AKY8" s="0"/>
-      <c r="AKZ8" s="0"/>
-      <c r="ALA8" s="0"/>
-      <c r="ALB8" s="0"/>
-      <c r="ALC8" s="0"/>
-      <c r="ALD8" s="0"/>
-      <c r="ALE8" s="0"/>
-      <c r="ALF8" s="0"/>
-      <c r="ALG8" s="0"/>
-      <c r="ALH8" s="0"/>
-      <c r="ALI8" s="0"/>
-      <c r="ALJ8" s="0"/>
-      <c r="ALK8" s="0"/>
-      <c r="ALL8" s="0"/>
-      <c r="ALM8" s="0"/>
-      <c r="ALN8" s="0"/>
-      <c r="ALO8" s="0"/>
-      <c r="ALP8" s="0"/>
-      <c r="ALQ8" s="0"/>
-      <c r="ALR8" s="0"/>
-      <c r="ALS8" s="0"/>
-      <c r="ALT8" s="0"/>
-      <c r="ALU8" s="0"/>
-      <c r="ALV8" s="0"/>
-      <c r="ALW8" s="0"/>
-      <c r="ALX8" s="0"/>
-      <c r="ALY8" s="0"/>
-      <c r="ALZ8" s="0"/>
-      <c r="AMA8" s="0"/>
-      <c r="AMB8" s="0"/>
-      <c r="AMC8" s="0"/>
-      <c r="AMD8" s="0"/>
-      <c r="AME8" s="0"/>
-      <c r="AMF8" s="0"/>
-      <c r="AMG8" s="0"/>
-      <c r="AMH8" s="0"/>
-      <c r="AMI8" s="0"/>
-      <c r="AMJ8" s="0"/>
-      <c r="AMK8" s="0"/>
-      <c r="AML8" s="0"/>
-      <c r="AMM8" s="0"/>
-    </row>
-    <row r="9" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AKM8" s="1"/>
+      <c r="AKN8" s="1"/>
+      <c r="AKO8" s="1"/>
+      <c r="AKP8" s="1"/>
+      <c r="AKQ8" s="1"/>
+      <c r="AKR8" s="1"/>
+      <c r="AKS8" s="1"/>
+      <c r="AKT8" s="1"/>
+      <c r="AKU8" s="1"/>
+      <c r="AKV8" s="1"/>
+      <c r="AKW8" s="1"/>
+      <c r="AKX8" s="1"/>
+      <c r="AKY8" s="1"/>
+      <c r="AKZ8" s="1"/>
+      <c r="ALA8" s="1"/>
+      <c r="ALB8" s="1"/>
+      <c r="ALC8" s="1"/>
+      <c r="ALD8" s="1"/>
+      <c r="ALE8" s="1"/>
+      <c r="ALF8" s="1"/>
+      <c r="ALG8" s="1"/>
+      <c r="ALH8" s="1"/>
+      <c r="ALI8" s="1"/>
+      <c r="ALJ8" s="1"/>
+      <c r="ALK8" s="1"/>
+      <c r="ALL8" s="1"/>
+      <c r="ALM8" s="1"/>
+      <c r="ALN8" s="1"/>
+      <c r="ALO8" s="1"/>
+      <c r="ALP8" s="1"/>
+      <c r="ALQ8" s="1"/>
+      <c r="ALR8" s="1"/>
+      <c r="ALS8" s="1"/>
+      <c r="ALT8" s="1"/>
+      <c r="ALU8" s="1"/>
+      <c r="ALV8" s="1"/>
+      <c r="ALW8" s="1"/>
+      <c r="ALX8" s="1"/>
+      <c r="ALY8" s="1"/>
+      <c r="ALZ8" s="1"/>
+      <c r="AMA8" s="1"/>
+      <c r="AMB8" s="1"/>
+      <c r="AMC8" s="1"/>
+      <c r="AMD8" s="1"/>
+      <c r="AME8" s="1"/>
+      <c r="AMF8" s="1"/>
+      <c r="AMG8" s="1"/>
+      <c r="AMH8" s="1"/>
+      <c r="AMI8" s="1"/>
+      <c r="AMJ8" s="1"/>
+      <c r="AMK8" s="1"/>
+      <c r="AML8" s="1"/>
+      <c r="AMM8" s="1"/>
+      <c r="AMN8" s="1"/>
+      <c r="AMO8" s="1"/>
+    </row>
+    <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AKL9" s="0"/>
-      <c r="AKM9" s="0"/>
-      <c r="AKN9" s="0"/>
-      <c r="AKO9" s="0"/>
-      <c r="AKP9" s="0"/>
-      <c r="AKQ9" s="0"/>
-      <c r="AKR9" s="0"/>
-      <c r="AKS9" s="0"/>
-      <c r="AKT9" s="0"/>
-      <c r="AKU9" s="0"/>
-      <c r="AKV9" s="0"/>
-      <c r="AKW9" s="0"/>
-      <c r="AKX9" s="0"/>
-      <c r="AKY9" s="0"/>
-      <c r="AKZ9" s="0"/>
-      <c r="ALA9" s="0"/>
-      <c r="ALB9" s="0"/>
-      <c r="ALC9" s="0"/>
-      <c r="ALD9" s="0"/>
-      <c r="ALE9" s="0"/>
-      <c r="ALF9" s="0"/>
-      <c r="ALG9" s="0"/>
-      <c r="ALH9" s="0"/>
-      <c r="ALI9" s="0"/>
-      <c r="ALJ9" s="0"/>
-      <c r="ALK9" s="0"/>
-      <c r="ALL9" s="0"/>
-      <c r="ALM9" s="0"/>
-      <c r="ALN9" s="0"/>
-      <c r="ALO9" s="0"/>
-      <c r="ALP9" s="0"/>
-      <c r="ALQ9" s="0"/>
-      <c r="ALR9" s="0"/>
-      <c r="ALS9" s="0"/>
-      <c r="ALT9" s="0"/>
-      <c r="ALU9" s="0"/>
-      <c r="ALV9" s="0"/>
-      <c r="ALW9" s="0"/>
-      <c r="ALX9" s="0"/>
-      <c r="ALY9" s="0"/>
-      <c r="ALZ9" s="0"/>
-      <c r="AMA9" s="0"/>
-      <c r="AMB9" s="0"/>
-      <c r="AMC9" s="0"/>
-      <c r="AMD9" s="0"/>
-      <c r="AME9" s="0"/>
-      <c r="AMF9" s="0"/>
-      <c r="AMG9" s="0"/>
-      <c r="AMH9" s="0"/>
-      <c r="AMI9" s="0"/>
-      <c r="AMJ9" s="0"/>
-      <c r="AMK9" s="0"/>
-      <c r="AML9" s="0"/>
-      <c r="AMM9" s="0"/>
-    </row>
-    <row r="10" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="AKL10" s="0"/>
-      <c r="AKM10" s="0"/>
-      <c r="AKN10" s="0"/>
-      <c r="AKO10" s="0"/>
-      <c r="AKP10" s="0"/>
-      <c r="AKQ10" s="0"/>
-      <c r="AKR10" s="0"/>
-      <c r="AKS10" s="0"/>
-      <c r="AKT10" s="0"/>
-      <c r="AKU10" s="0"/>
-      <c r="AKV10" s="0"/>
-      <c r="AKW10" s="0"/>
-      <c r="AKX10" s="0"/>
-      <c r="AKY10" s="0"/>
-      <c r="AKZ10" s="0"/>
-      <c r="ALA10" s="0"/>
-      <c r="ALB10" s="0"/>
-      <c r="ALC10" s="0"/>
-      <c r="ALD10" s="0"/>
-      <c r="ALE10" s="0"/>
-      <c r="ALF10" s="0"/>
-      <c r="ALG10" s="0"/>
-      <c r="ALH10" s="0"/>
-      <c r="ALI10" s="0"/>
-      <c r="ALJ10" s="0"/>
-      <c r="ALK10" s="0"/>
-      <c r="ALL10" s="0"/>
-      <c r="ALM10" s="0"/>
-      <c r="ALN10" s="0"/>
-      <c r="ALO10" s="0"/>
-      <c r="ALP10" s="0"/>
-      <c r="ALQ10" s="0"/>
-      <c r="ALR10" s="0"/>
-      <c r="ALS10" s="0"/>
-      <c r="ALT10" s="0"/>
-      <c r="ALU10" s="0"/>
-      <c r="ALV10" s="0"/>
-      <c r="ALW10" s="0"/>
-      <c r="ALX10" s="0"/>
-      <c r="ALY10" s="0"/>
-      <c r="ALZ10" s="0"/>
-      <c r="AMA10" s="0"/>
-      <c r="AMB10" s="0"/>
-      <c r="AMC10" s="0"/>
-      <c r="AMD10" s="0"/>
-      <c r="AME10" s="0"/>
-      <c r="AMF10" s="0"/>
-      <c r="AMG10" s="0"/>
-      <c r="AMH10" s="0"/>
-      <c r="AMI10" s="0"/>
-      <c r="AMJ10" s="0"/>
-      <c r="AMK10" s="0"/>
-      <c r="AML10" s="0"/>
-      <c r="AMM10" s="0"/>
-    </row>
-    <row r="11" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AKL11" s="0"/>
-      <c r="AKM11" s="0"/>
-      <c r="AKN11" s="0"/>
-      <c r="AKO11" s="0"/>
-      <c r="AKP11" s="0"/>
-      <c r="AKQ11" s="0"/>
-      <c r="AKR11" s="0"/>
-      <c r="AKS11" s="0"/>
-      <c r="AKT11" s="0"/>
-      <c r="AKU11" s="0"/>
-      <c r="AKV11" s="0"/>
-      <c r="AKW11" s="0"/>
-      <c r="AKX11" s="0"/>
-      <c r="AKY11" s="0"/>
-      <c r="AKZ11" s="0"/>
-      <c r="ALA11" s="0"/>
-      <c r="ALB11" s="0"/>
-      <c r="ALC11" s="0"/>
-      <c r="ALD11" s="0"/>
-      <c r="ALE11" s="0"/>
-      <c r="ALF11" s="0"/>
-      <c r="ALG11" s="0"/>
-      <c r="ALH11" s="0"/>
-      <c r="ALI11" s="0"/>
-      <c r="ALJ11" s="0"/>
-      <c r="ALK11" s="0"/>
-      <c r="ALL11" s="0"/>
-      <c r="ALM11" s="0"/>
-      <c r="ALN11" s="0"/>
-      <c r="ALO11" s="0"/>
-      <c r="ALP11" s="0"/>
-      <c r="ALQ11" s="0"/>
-      <c r="ALR11" s="0"/>
-      <c r="ALS11" s="0"/>
-      <c r="ALT11" s="0"/>
-      <c r="ALU11" s="0"/>
-      <c r="ALV11" s="0"/>
-      <c r="ALW11" s="0"/>
-      <c r="ALX11" s="0"/>
-      <c r="ALY11" s="0"/>
-      <c r="ALZ11" s="0"/>
-      <c r="AMA11" s="0"/>
-      <c r="AMB11" s="0"/>
-      <c r="AMC11" s="0"/>
-      <c r="AMD11" s="0"/>
-      <c r="AME11" s="0"/>
-      <c r="AMF11" s="0"/>
-      <c r="AMG11" s="0"/>
-      <c r="AMH11" s="0"/>
-      <c r="AMI11" s="0"/>
-      <c r="AMJ11" s="0"/>
-      <c r="AMK11" s="0"/>
-      <c r="AML11" s="0"/>
-      <c r="AMM11" s="0"/>
-    </row>
-    <row r="12" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AKK12" s="1"/>
-      <c r="AKL12" s="0"/>
-      <c r="AKM12" s="0"/>
-      <c r="AKN12" s="0"/>
-      <c r="AKO12" s="0"/>
-      <c r="AKP12" s="0"/>
-      <c r="AKQ12" s="0"/>
-      <c r="AKR12" s="0"/>
-      <c r="AKS12" s="0"/>
-      <c r="AKT12" s="0"/>
-      <c r="AKU12" s="0"/>
-      <c r="AKV12" s="0"/>
-      <c r="AKW12" s="0"/>
-      <c r="AKX12" s="0"/>
-      <c r="AKY12" s="0"/>
-      <c r="AKZ12" s="0"/>
-      <c r="ALA12" s="0"/>
-      <c r="ALB12" s="0"/>
-      <c r="ALC12" s="0"/>
-      <c r="ALD12" s="0"/>
-      <c r="ALE12" s="0"/>
-      <c r="ALF12" s="0"/>
-      <c r="ALG12" s="0"/>
-      <c r="ALH12" s="0"/>
-      <c r="ALI12" s="0"/>
-      <c r="ALJ12" s="0"/>
-      <c r="ALK12" s="0"/>
-      <c r="ALL12" s="0"/>
-      <c r="ALM12" s="0"/>
-      <c r="ALN12" s="0"/>
-      <c r="ALO12" s="0"/>
-      <c r="ALP12" s="0"/>
-      <c r="ALQ12" s="0"/>
-      <c r="ALR12" s="0"/>
-      <c r="ALS12" s="0"/>
-      <c r="ALT12" s="0"/>
-      <c r="ALU12" s="0"/>
-      <c r="ALV12" s="0"/>
-      <c r="ALW12" s="0"/>
-      <c r="ALX12" s="0"/>
-      <c r="ALY12" s="0"/>
-      <c r="ALZ12" s="0"/>
-      <c r="AMA12" s="0"/>
-      <c r="AMB12" s="0"/>
-      <c r="AMC12" s="0"/>
-      <c r="AMD12" s="0"/>
-      <c r="AME12" s="0"/>
-      <c r="AMF12" s="0"/>
-      <c r="AMG12" s="0"/>
-      <c r="AMH12" s="0"/>
-      <c r="AMI12" s="0"/>
-      <c r="AMJ12" s="0"/>
-      <c r="AMK12" s="0"/>
-      <c r="AML12" s="0"/>
-      <c r="AMM12" s="0"/>
-    </row>
-    <row r="13" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>36</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AKM12" s="1"/>
+      <c r="AKN12" s="1"/>
+      <c r="AKO12" s="1"/>
+      <c r="AKP12" s="1"/>
+      <c r="AKQ12" s="1"/>
+      <c r="AKR12" s="1"/>
+      <c r="AKS12" s="1"/>
+      <c r="AKT12" s="1"/>
+      <c r="AKU12" s="1"/>
+      <c r="AKV12" s="1"/>
+      <c r="AKW12" s="1"/>
+      <c r="AKX12" s="1"/>
+      <c r="AKY12" s="1"/>
+      <c r="AKZ12" s="1"/>
+      <c r="ALA12" s="1"/>
+      <c r="ALB12" s="1"/>
+      <c r="ALC12" s="1"/>
+      <c r="ALD12" s="1"/>
+      <c r="ALE12" s="1"/>
+      <c r="ALF12" s="1"/>
+      <c r="ALG12" s="1"/>
+      <c r="ALH12" s="1"/>
+      <c r="ALI12" s="1"/>
+      <c r="ALJ12" s="1"/>
+      <c r="ALK12" s="1"/>
+      <c r="ALL12" s="1"/>
+      <c r="ALM12" s="1"/>
+      <c r="ALN12" s="1"/>
+      <c r="ALO12" s="1"/>
+      <c r="ALP12" s="1"/>
+      <c r="ALQ12" s="1"/>
+      <c r="ALR12" s="1"/>
+      <c r="ALS12" s="1"/>
+      <c r="ALT12" s="1"/>
+      <c r="ALU12" s="1"/>
+      <c r="ALV12" s="1"/>
+      <c r="ALW12" s="1"/>
+      <c r="ALX12" s="1"/>
+      <c r="ALY12" s="1"/>
+      <c r="ALZ12" s="1"/>
+      <c r="AMA12" s="1"/>
+      <c r="AMB12" s="1"/>
+      <c r="AMC12" s="1"/>
+      <c r="AMD12" s="1"/>
+      <c r="AME12" s="1"/>
+      <c r="AMF12" s="1"/>
+      <c r="AMG12" s="1"/>
+      <c r="AMH12" s="1"/>
+      <c r="AMI12" s="1"/>
+      <c r="AMJ12" s="1"/>
+      <c r="AMK12" s="1"/>
+      <c r="AML12" s="1"/>
+      <c r="AMM12" s="1"/>
+      <c r="AMN12" s="1"/>
+      <c r="AMO12" s="1"/>
+    </row>
+    <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AKL13" s="0"/>
-      <c r="AKM13" s="0"/>
-      <c r="AKN13" s="0"/>
-      <c r="AKO13" s="0"/>
-      <c r="AKP13" s="0"/>
-      <c r="AKQ13" s="0"/>
-      <c r="AKR13" s="0"/>
-      <c r="AKS13" s="0"/>
-      <c r="AKT13" s="0"/>
-      <c r="AKU13" s="0"/>
-      <c r="AKV13" s="0"/>
-      <c r="AKW13" s="0"/>
-      <c r="AKX13" s="0"/>
-      <c r="AKY13" s="0"/>
-      <c r="AKZ13" s="0"/>
-      <c r="ALA13" s="0"/>
-      <c r="ALB13" s="0"/>
-      <c r="ALC13" s="0"/>
-      <c r="ALD13" s="0"/>
-      <c r="ALE13" s="0"/>
-      <c r="ALF13" s="0"/>
-      <c r="ALG13" s="0"/>
-      <c r="ALH13" s="0"/>
-      <c r="ALI13" s="0"/>
-      <c r="ALJ13" s="0"/>
-      <c r="ALK13" s="0"/>
-      <c r="ALL13" s="0"/>
-      <c r="ALM13" s="0"/>
-      <c r="ALN13" s="0"/>
-      <c r="ALO13" s="0"/>
-      <c r="ALP13" s="0"/>
-      <c r="ALQ13" s="0"/>
-      <c r="ALR13" s="0"/>
-      <c r="ALS13" s="0"/>
-      <c r="ALT13" s="0"/>
-      <c r="ALU13" s="0"/>
-      <c r="ALV13" s="0"/>
-      <c r="ALW13" s="0"/>
-      <c r="ALX13" s="0"/>
-      <c r="ALY13" s="0"/>
-      <c r="ALZ13" s="0"/>
-      <c r="AMA13" s="0"/>
-      <c r="AMB13" s="0"/>
-      <c r="AMC13" s="0"/>
-      <c r="AMD13" s="0"/>
-      <c r="AME13" s="0"/>
-      <c r="AMF13" s="0"/>
-      <c r="AMG13" s="0"/>
-      <c r="AMH13" s="0"/>
-      <c r="AMI13" s="0"/>
-      <c r="AMJ13" s="0"/>
-      <c r="AMK13" s="0"/>
-      <c r="AML13" s="0"/>
-      <c r="AMM13" s="0"/>
-    </row>
-    <row r="14" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="AKL14" s="0"/>
-      <c r="AKM14" s="0"/>
-      <c r="AKN14" s="0"/>
-      <c r="AKO14" s="0"/>
-      <c r="AKP14" s="0"/>
-      <c r="AKQ14" s="0"/>
-      <c r="AKR14" s="0"/>
-      <c r="AKS14" s="0"/>
-      <c r="AKT14" s="0"/>
-      <c r="AKU14" s="0"/>
-      <c r="AKV14" s="0"/>
-      <c r="AKW14" s="0"/>
-      <c r="AKX14" s="0"/>
-      <c r="AKY14" s="0"/>
-      <c r="AKZ14" s="0"/>
-      <c r="ALA14" s="0"/>
-      <c r="ALB14" s="0"/>
-      <c r="ALC14" s="0"/>
-      <c r="ALD14" s="0"/>
-      <c r="ALE14" s="0"/>
-      <c r="ALF14" s="0"/>
-      <c r="ALG14" s="0"/>
-      <c r="ALH14" s="0"/>
-      <c r="ALI14" s="0"/>
-      <c r="ALJ14" s="0"/>
-      <c r="ALK14" s="0"/>
-      <c r="ALL14" s="0"/>
-      <c r="ALM14" s="0"/>
-      <c r="ALN14" s="0"/>
-      <c r="ALO14" s="0"/>
-      <c r="ALP14" s="0"/>
-      <c r="ALQ14" s="0"/>
-      <c r="ALR14" s="0"/>
-      <c r="ALS14" s="0"/>
-      <c r="ALT14" s="0"/>
-      <c r="ALU14" s="0"/>
-      <c r="ALV14" s="0"/>
-      <c r="ALW14" s="0"/>
-      <c r="ALX14" s="0"/>
-      <c r="ALY14" s="0"/>
-      <c r="ALZ14" s="0"/>
-      <c r="AMA14" s="0"/>
-      <c r="AMB14" s="0"/>
-      <c r="AMC14" s="0"/>
-      <c r="AMD14" s="0"/>
-      <c r="AME14" s="0"/>
-      <c r="AMF14" s="0"/>
-      <c r="AMG14" s="0"/>
-      <c r="AMH14" s="0"/>
-      <c r="AMI14" s="0"/>
-      <c r="AMJ14" s="0"/>
-      <c r="AMK14" s="0"/>
-      <c r="AML14" s="0"/>
-      <c r="AMM14" s="0"/>
-    </row>
-    <row r="15" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>42</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AKK15" s="1"/>
-      <c r="AKL15" s="0"/>
-      <c r="AKM15" s="0"/>
-      <c r="AKN15" s="0"/>
-      <c r="AKO15" s="0"/>
-      <c r="AKP15" s="0"/>
-      <c r="AKQ15" s="0"/>
-      <c r="AKR15" s="0"/>
-      <c r="AKS15" s="0"/>
-      <c r="AKT15" s="0"/>
-      <c r="AKU15" s="0"/>
-      <c r="AKV15" s="0"/>
-      <c r="AKW15" s="0"/>
-      <c r="AKX15" s="0"/>
-      <c r="AKY15" s="0"/>
-      <c r="AKZ15" s="0"/>
-      <c r="ALA15" s="0"/>
-      <c r="ALB15" s="0"/>
-      <c r="ALC15" s="0"/>
-      <c r="ALD15" s="0"/>
-      <c r="ALE15" s="0"/>
-      <c r="ALF15" s="0"/>
-      <c r="ALG15" s="0"/>
-      <c r="ALH15" s="0"/>
-      <c r="ALI15" s="0"/>
-      <c r="ALJ15" s="0"/>
-      <c r="ALK15" s="0"/>
-      <c r="ALL15" s="0"/>
-      <c r="ALM15" s="0"/>
-      <c r="ALN15" s="0"/>
-      <c r="ALO15" s="0"/>
-      <c r="ALP15" s="0"/>
-      <c r="ALQ15" s="0"/>
-      <c r="ALR15" s="0"/>
-      <c r="ALS15" s="0"/>
-      <c r="ALT15" s="0"/>
-      <c r="ALU15" s="0"/>
-      <c r="ALV15" s="0"/>
-      <c r="ALW15" s="0"/>
-      <c r="ALX15" s="0"/>
-      <c r="ALY15" s="0"/>
-      <c r="ALZ15" s="0"/>
-      <c r="AMA15" s="0"/>
-      <c r="AMB15" s="0"/>
-      <c r="AMC15" s="0"/>
-      <c r="AMD15" s="0"/>
-      <c r="AME15" s="0"/>
-      <c r="AMF15" s="0"/>
-      <c r="AMG15" s="0"/>
-      <c r="AMH15" s="0"/>
-      <c r="AMI15" s="0"/>
-      <c r="AMJ15" s="0"/>
-      <c r="AMK15" s="0"/>
-      <c r="AML15" s="0"/>
-      <c r="AMM15" s="0"/>
-    </row>
-    <row r="16" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>45</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AKM15" s="1"/>
+      <c r="AKN15" s="1"/>
+      <c r="AKO15" s="1"/>
+      <c r="AKP15" s="1"/>
+      <c r="AKQ15" s="1"/>
+      <c r="AKR15" s="1"/>
+      <c r="AKS15" s="1"/>
+      <c r="AKT15" s="1"/>
+      <c r="AKU15" s="1"/>
+      <c r="AKV15" s="1"/>
+      <c r="AKW15" s="1"/>
+      <c r="AKX15" s="1"/>
+      <c r="AKY15" s="1"/>
+      <c r="AKZ15" s="1"/>
+      <c r="ALA15" s="1"/>
+      <c r="ALB15" s="1"/>
+      <c r="ALC15" s="1"/>
+      <c r="ALD15" s="1"/>
+      <c r="ALE15" s="1"/>
+      <c r="ALF15" s="1"/>
+      <c r="ALG15" s="1"/>
+      <c r="ALH15" s="1"/>
+      <c r="ALI15" s="1"/>
+      <c r="ALJ15" s="1"/>
+      <c r="ALK15" s="1"/>
+      <c r="ALL15" s="1"/>
+      <c r="ALM15" s="1"/>
+      <c r="ALN15" s="1"/>
+      <c r="ALO15" s="1"/>
+      <c r="ALP15" s="1"/>
+      <c r="ALQ15" s="1"/>
+      <c r="ALR15" s="1"/>
+      <c r="ALS15" s="1"/>
+      <c r="ALT15" s="1"/>
+      <c r="ALU15" s="1"/>
+      <c r="ALV15" s="1"/>
+      <c r="ALW15" s="1"/>
+      <c r="ALX15" s="1"/>
+      <c r="ALY15" s="1"/>
+      <c r="ALZ15" s="1"/>
+      <c r="AMA15" s="1"/>
+      <c r="AMB15" s="1"/>
+      <c r="AMC15" s="1"/>
+      <c r="AMD15" s="1"/>
+      <c r="AME15" s="1"/>
+      <c r="AMF15" s="1"/>
+      <c r="AMG15" s="1"/>
+      <c r="AMH15" s="1"/>
+      <c r="AMI15" s="1"/>
+      <c r="AMJ15" s="1"/>
+      <c r="AMK15" s="1"/>
+      <c r="AML15" s="1"/>
+      <c r="AMM15" s="1"/>
+      <c r="AMN15" s="1"/>
+      <c r="AMO15" s="1"/>
+    </row>
+    <row r="16" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AKL16" s="0"/>
-      <c r="AKM16" s="0"/>
-      <c r="AKN16" s="0"/>
-      <c r="AKO16" s="0"/>
-      <c r="AKP16" s="0"/>
-      <c r="AKQ16" s="0"/>
-      <c r="AKR16" s="0"/>
-      <c r="AKS16" s="0"/>
-      <c r="AKT16" s="0"/>
-      <c r="AKU16" s="0"/>
-      <c r="AKV16" s="0"/>
-      <c r="AKW16" s="0"/>
-      <c r="AKX16" s="0"/>
-      <c r="AKY16" s="0"/>
-      <c r="AKZ16" s="0"/>
-      <c r="ALA16" s="0"/>
-      <c r="ALB16" s="0"/>
-      <c r="ALC16" s="0"/>
-      <c r="ALD16" s="0"/>
-      <c r="ALE16" s="0"/>
-      <c r="ALF16" s="0"/>
-      <c r="ALG16" s="0"/>
-      <c r="ALH16" s="0"/>
-      <c r="ALI16" s="0"/>
-      <c r="ALJ16" s="0"/>
-      <c r="ALK16" s="0"/>
-      <c r="ALL16" s="0"/>
-      <c r="ALM16" s="0"/>
-      <c r="ALN16" s="0"/>
-      <c r="ALO16" s="0"/>
-      <c r="ALP16" s="0"/>
-      <c r="ALQ16" s="0"/>
-      <c r="ALR16" s="0"/>
-      <c r="ALS16" s="0"/>
-      <c r="ALT16" s="0"/>
-      <c r="ALU16" s="0"/>
-      <c r="ALV16" s="0"/>
-      <c r="ALW16" s="0"/>
-      <c r="ALX16" s="0"/>
-      <c r="ALY16" s="0"/>
-      <c r="ALZ16" s="0"/>
-      <c r="AMA16" s="0"/>
-      <c r="AMB16" s="0"/>
-      <c r="AMC16" s="0"/>
-      <c r="AMD16" s="0"/>
-      <c r="AME16" s="0"/>
-      <c r="AMF16" s="0"/>
-      <c r="AMG16" s="0"/>
-      <c r="AMH16" s="0"/>
-      <c r="AMI16" s="0"/>
-      <c r="AMJ16" s="0"/>
-      <c r="AMK16" s="0"/>
-      <c r="AML16" s="0"/>
-      <c r="AMM16" s="0"/>
-    </row>
-    <row r="17" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>48</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AKL17" s="0"/>
-      <c r="AKM17" s="0"/>
-      <c r="AKN17" s="0"/>
-      <c r="AKO17" s="0"/>
-      <c r="AKP17" s="0"/>
-      <c r="AKQ17" s="0"/>
-      <c r="AKR17" s="0"/>
-      <c r="AKS17" s="0"/>
-      <c r="AKT17" s="0"/>
-      <c r="AKU17" s="0"/>
-      <c r="AKV17" s="0"/>
-      <c r="AKW17" s="0"/>
-      <c r="AKX17" s="0"/>
-      <c r="AKY17" s="0"/>
-      <c r="AKZ17" s="0"/>
-      <c r="ALA17" s="0"/>
-      <c r="ALB17" s="0"/>
-      <c r="ALC17" s="0"/>
-      <c r="ALD17" s="0"/>
-      <c r="ALE17" s="0"/>
-      <c r="ALF17" s="0"/>
-      <c r="ALG17" s="0"/>
-      <c r="ALH17" s="0"/>
-      <c r="ALI17" s="0"/>
-      <c r="ALJ17" s="0"/>
-      <c r="ALK17" s="0"/>
-      <c r="ALL17" s="0"/>
-      <c r="ALM17" s="0"/>
-      <c r="ALN17" s="0"/>
-      <c r="ALO17" s="0"/>
-      <c r="ALP17" s="0"/>
-      <c r="ALQ17" s="0"/>
-      <c r="ALR17" s="0"/>
-      <c r="ALS17" s="0"/>
-      <c r="ALT17" s="0"/>
-      <c r="ALU17" s="0"/>
-      <c r="ALV17" s="0"/>
-      <c r="ALW17" s="0"/>
-      <c r="ALX17" s="0"/>
-      <c r="ALY17" s="0"/>
-      <c r="ALZ17" s="0"/>
-      <c r="AMA17" s="0"/>
-      <c r="AMB17" s="0"/>
-      <c r="AMC17" s="0"/>
-      <c r="AMD17" s="0"/>
-      <c r="AME17" s="0"/>
-      <c r="AMF17" s="0"/>
-      <c r="AMG17" s="0"/>
-      <c r="AMH17" s="0"/>
-      <c r="AMI17" s="0"/>
-      <c r="AMJ17" s="0"/>
-      <c r="AMK17" s="0"/>
-      <c r="AML17" s="0"/>
-      <c r="AMM17" s="0"/>
-    </row>
-    <row r="18" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>51</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AKK18" s="1"/>
-      <c r="AKL18" s="0"/>
-      <c r="AKM18" s="0"/>
-      <c r="AKN18" s="0"/>
-      <c r="AKO18" s="0"/>
-      <c r="AKP18" s="0"/>
-      <c r="AKQ18" s="0"/>
-      <c r="AKR18" s="0"/>
-      <c r="AKS18" s="0"/>
-      <c r="AKT18" s="0"/>
-      <c r="AKU18" s="0"/>
-      <c r="AKV18" s="0"/>
-      <c r="AKW18" s="0"/>
-      <c r="AKX18" s="0"/>
-      <c r="AKY18" s="0"/>
-      <c r="AKZ18" s="0"/>
-      <c r="ALA18" s="0"/>
-      <c r="ALB18" s="0"/>
-      <c r="ALC18" s="0"/>
-      <c r="ALD18" s="0"/>
-      <c r="ALE18" s="0"/>
-      <c r="ALF18" s="0"/>
-      <c r="ALG18" s="0"/>
-      <c r="ALH18" s="0"/>
-      <c r="ALI18" s="0"/>
-      <c r="ALJ18" s="0"/>
-      <c r="ALK18" s="0"/>
-      <c r="ALL18" s="0"/>
-      <c r="ALM18" s="0"/>
-      <c r="ALN18" s="0"/>
-      <c r="ALO18" s="0"/>
-      <c r="ALP18" s="0"/>
-      <c r="ALQ18" s="0"/>
-      <c r="ALR18" s="0"/>
-      <c r="ALS18" s="0"/>
-      <c r="ALT18" s="0"/>
-      <c r="ALU18" s="0"/>
-      <c r="ALV18" s="0"/>
-      <c r="ALW18" s="0"/>
-      <c r="ALX18" s="0"/>
-      <c r="ALY18" s="0"/>
-      <c r="ALZ18" s="0"/>
-      <c r="AMA18" s="0"/>
-      <c r="AMB18" s="0"/>
-      <c r="AMC18" s="0"/>
-      <c r="AMD18" s="0"/>
-      <c r="AME18" s="0"/>
-      <c r="AMF18" s="0"/>
-      <c r="AMG18" s="0"/>
-      <c r="AMH18" s="0"/>
-      <c r="AMI18" s="0"/>
-      <c r="AMJ18" s="0"/>
-      <c r="AMK18" s="0"/>
-      <c r="AML18" s="0"/>
-      <c r="AMM18" s="0"/>
-    </row>
-    <row r="19" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AKM18" s="1"/>
+      <c r="AKN18" s="1"/>
+      <c r="AKO18" s="1"/>
+      <c r="AKP18" s="1"/>
+      <c r="AKQ18" s="1"/>
+      <c r="AKR18" s="1"/>
+      <c r="AKS18" s="1"/>
+      <c r="AKT18" s="1"/>
+      <c r="AKU18" s="1"/>
+      <c r="AKV18" s="1"/>
+      <c r="AKW18" s="1"/>
+      <c r="AKX18" s="1"/>
+      <c r="AKY18" s="1"/>
+      <c r="AKZ18" s="1"/>
+      <c r="ALA18" s="1"/>
+      <c r="ALB18" s="1"/>
+      <c r="ALC18" s="1"/>
+      <c r="ALD18" s="1"/>
+      <c r="ALE18" s="1"/>
+      <c r="ALF18" s="1"/>
+      <c r="ALG18" s="1"/>
+      <c r="ALH18" s="1"/>
+      <c r="ALI18" s="1"/>
+      <c r="ALJ18" s="1"/>
+      <c r="ALK18" s="1"/>
+      <c r="ALL18" s="1"/>
+      <c r="ALM18" s="1"/>
+      <c r="ALN18" s="1"/>
+      <c r="ALO18" s="1"/>
+      <c r="ALP18" s="1"/>
+      <c r="ALQ18" s="1"/>
+      <c r="ALR18" s="1"/>
+      <c r="ALS18" s="1"/>
+      <c r="ALT18" s="1"/>
+      <c r="ALU18" s="1"/>
+      <c r="ALV18" s="1"/>
+      <c r="ALW18" s="1"/>
+      <c r="ALX18" s="1"/>
+      <c r="ALY18" s="1"/>
+      <c r="ALZ18" s="1"/>
+      <c r="AMA18" s="1"/>
+      <c r="AMB18" s="1"/>
+      <c r="AMC18" s="1"/>
+      <c r="AMD18" s="1"/>
+      <c r="AME18" s="1"/>
+      <c r="AMF18" s="1"/>
+      <c r="AMG18" s="1"/>
+      <c r="AMH18" s="1"/>
+      <c r="AMI18" s="1"/>
+      <c r="AMJ18" s="1"/>
+      <c r="AMK18" s="1"/>
+      <c r="AML18" s="1"/>
+      <c r="AMM18" s="1"/>
+      <c r="AMN18" s="1"/>
+      <c r="AMO18" s="1"/>
+    </row>
+    <row r="19" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AKK19" s="1"/>
-      <c r="AKL19" s="0"/>
-      <c r="AKM19" s="0"/>
-      <c r="AKN19" s="0"/>
-      <c r="AKO19" s="0"/>
-      <c r="AKP19" s="0"/>
-      <c r="AKQ19" s="0"/>
-      <c r="AKR19" s="0"/>
-      <c r="AKS19" s="0"/>
-      <c r="AKT19" s="0"/>
-      <c r="AKU19" s="0"/>
-      <c r="AKV19" s="0"/>
-      <c r="AKW19" s="0"/>
-      <c r="AKX19" s="0"/>
-      <c r="AKY19" s="0"/>
-      <c r="AKZ19" s="0"/>
-      <c r="ALA19" s="0"/>
-      <c r="ALB19" s="0"/>
-      <c r="ALC19" s="0"/>
-      <c r="ALD19" s="0"/>
-      <c r="ALE19" s="0"/>
-      <c r="ALF19" s="0"/>
-      <c r="ALG19" s="0"/>
-      <c r="ALH19" s="0"/>
-      <c r="ALI19" s="0"/>
-      <c r="ALJ19" s="0"/>
-      <c r="ALK19" s="0"/>
-      <c r="ALL19" s="0"/>
-      <c r="ALM19" s="0"/>
-      <c r="ALN19" s="0"/>
-      <c r="ALO19" s="0"/>
-      <c r="ALP19" s="0"/>
-      <c r="ALQ19" s="0"/>
-      <c r="ALR19" s="0"/>
-      <c r="ALS19" s="0"/>
-      <c r="ALT19" s="0"/>
-      <c r="ALU19" s="0"/>
-      <c r="ALV19" s="0"/>
-      <c r="ALW19" s="0"/>
-      <c r="ALX19" s="0"/>
-      <c r="ALY19" s="0"/>
-      <c r="ALZ19" s="0"/>
-      <c r="AMA19" s="0"/>
-      <c r="AMB19" s="0"/>
-      <c r="AMC19" s="0"/>
-      <c r="AMD19" s="0"/>
-      <c r="AME19" s="0"/>
-      <c r="AMF19" s="0"/>
-      <c r="AMG19" s="0"/>
-      <c r="AMH19" s="0"/>
-      <c r="AMI19" s="0"/>
-      <c r="AMJ19" s="0"/>
-      <c r="AMK19" s="0"/>
-      <c r="AML19" s="0"/>
-      <c r="AMM19" s="0"/>
-    </row>
-    <row r="20" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>57</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AKM19" s="1"/>
+      <c r="AKN19" s="1"/>
+      <c r="AKO19" s="1"/>
+      <c r="AKP19" s="1"/>
+      <c r="AKQ19" s="1"/>
+      <c r="AKR19" s="1"/>
+      <c r="AKS19" s="1"/>
+      <c r="AKT19" s="1"/>
+      <c r="AKU19" s="1"/>
+      <c r="AKV19" s="1"/>
+      <c r="AKW19" s="1"/>
+      <c r="AKX19" s="1"/>
+      <c r="AKY19" s="1"/>
+      <c r="AKZ19" s="1"/>
+      <c r="ALA19" s="1"/>
+      <c r="ALB19" s="1"/>
+      <c r="ALC19" s="1"/>
+      <c r="ALD19" s="1"/>
+      <c r="ALE19" s="1"/>
+      <c r="ALF19" s="1"/>
+      <c r="ALG19" s="1"/>
+      <c r="ALH19" s="1"/>
+      <c r="ALI19" s="1"/>
+      <c r="ALJ19" s="1"/>
+      <c r="ALK19" s="1"/>
+      <c r="ALL19" s="1"/>
+      <c r="ALM19" s="1"/>
+      <c r="ALN19" s="1"/>
+      <c r="ALO19" s="1"/>
+      <c r="ALP19" s="1"/>
+      <c r="ALQ19" s="1"/>
+      <c r="ALR19" s="1"/>
+      <c r="ALS19" s="1"/>
+      <c r="ALT19" s="1"/>
+      <c r="ALU19" s="1"/>
+      <c r="ALV19" s="1"/>
+      <c r="ALW19" s="1"/>
+      <c r="ALX19" s="1"/>
+      <c r="ALY19" s="1"/>
+      <c r="ALZ19" s="1"/>
+      <c r="AMA19" s="1"/>
+      <c r="AMB19" s="1"/>
+      <c r="AMC19" s="1"/>
+      <c r="AMD19" s="1"/>
+      <c r="AME19" s="1"/>
+      <c r="AMF19" s="1"/>
+      <c r="AMG19" s="1"/>
+      <c r="AMH19" s="1"/>
+      <c r="AMI19" s="1"/>
+      <c r="AMJ19" s="1"/>
+      <c r="AMK19" s="1"/>
+      <c r="AML19" s="1"/>
+      <c r="AMM19" s="1"/>
+      <c r="AMN19" s="1"/>
+      <c r="AMO19" s="1"/>
+    </row>
+    <row r="20" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AKL20" s="0"/>
-      <c r="AKM20" s="0"/>
-      <c r="AKN20" s="0"/>
-      <c r="AKO20" s="0"/>
-      <c r="AKP20" s="0"/>
-      <c r="AKQ20" s="0"/>
-      <c r="AKR20" s="0"/>
-      <c r="AKS20" s="0"/>
-      <c r="AKT20" s="0"/>
-      <c r="AKU20" s="0"/>
-      <c r="AKV20" s="0"/>
-      <c r="AKW20" s="0"/>
-      <c r="AKX20" s="0"/>
-      <c r="AKY20" s="0"/>
-      <c r="AKZ20" s="0"/>
-      <c r="ALA20" s="0"/>
-      <c r="ALB20" s="0"/>
-      <c r="ALC20" s="0"/>
-      <c r="ALD20" s="0"/>
-      <c r="ALE20" s="0"/>
-      <c r="ALF20" s="0"/>
-      <c r="ALG20" s="0"/>
-      <c r="ALH20" s="0"/>
-      <c r="ALI20" s="0"/>
-      <c r="ALJ20" s="0"/>
-      <c r="ALK20" s="0"/>
-      <c r="ALL20" s="0"/>
-      <c r="ALM20" s="0"/>
-      <c r="ALN20" s="0"/>
-      <c r="ALO20" s="0"/>
-      <c r="ALP20" s="0"/>
-      <c r="ALQ20" s="0"/>
-      <c r="ALR20" s="0"/>
-      <c r="ALS20" s="0"/>
-      <c r="ALT20" s="0"/>
-      <c r="ALU20" s="0"/>
-      <c r="ALV20" s="0"/>
-      <c r="ALW20" s="0"/>
-      <c r="ALX20" s="0"/>
-      <c r="ALY20" s="0"/>
-      <c r="ALZ20" s="0"/>
-      <c r="AMA20" s="0"/>
-      <c r="AMB20" s="0"/>
-      <c r="AMC20" s="0"/>
-      <c r="AMD20" s="0"/>
-      <c r="AME20" s="0"/>
-      <c r="AMF20" s="0"/>
-      <c r="AMG20" s="0"/>
-      <c r="AMH20" s="0"/>
-      <c r="AMI20" s="0"/>
-      <c r="AMJ20" s="0"/>
-      <c r="AMK20" s="0"/>
-      <c r="AML20" s="0"/>
-      <c r="AMM20" s="0"/>
-    </row>
-    <row r="21" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>60</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AKL21" s="0"/>
-      <c r="AKM21" s="0"/>
-      <c r="AKN21" s="0"/>
-      <c r="AKO21" s="0"/>
-      <c r="AKP21" s="0"/>
-      <c r="AKQ21" s="0"/>
-      <c r="AKR21" s="0"/>
-      <c r="AKS21" s="0"/>
-      <c r="AKT21" s="0"/>
-      <c r="AKU21" s="0"/>
-      <c r="AKV21" s="0"/>
-      <c r="AKW21" s="0"/>
-      <c r="AKX21" s="0"/>
-      <c r="AKY21" s="0"/>
-      <c r="AKZ21" s="0"/>
-      <c r="ALA21" s="0"/>
-      <c r="ALB21" s="0"/>
-      <c r="ALC21" s="0"/>
-      <c r="ALD21" s="0"/>
-      <c r="ALE21" s="0"/>
-      <c r="ALF21" s="0"/>
-      <c r="ALG21" s="0"/>
-      <c r="ALH21" s="0"/>
-      <c r="ALI21" s="0"/>
-      <c r="ALJ21" s="0"/>
-      <c r="ALK21" s="0"/>
-      <c r="ALL21" s="0"/>
-      <c r="ALM21" s="0"/>
-      <c r="ALN21" s="0"/>
-      <c r="ALO21" s="0"/>
-      <c r="ALP21" s="0"/>
-      <c r="ALQ21" s="0"/>
-      <c r="ALR21" s="0"/>
-      <c r="ALS21" s="0"/>
-      <c r="ALT21" s="0"/>
-      <c r="ALU21" s="0"/>
-      <c r="ALV21" s="0"/>
-      <c r="ALW21" s="0"/>
-      <c r="ALX21" s="0"/>
-      <c r="ALY21" s="0"/>
-      <c r="ALZ21" s="0"/>
-      <c r="AMA21" s="0"/>
-      <c r="AMB21" s="0"/>
-      <c r="AMC21" s="0"/>
-      <c r="AMD21" s="0"/>
-      <c r="AME21" s="0"/>
-      <c r="AMF21" s="0"/>
-      <c r="AMG21" s="0"/>
-      <c r="AMH21" s="0"/>
-      <c r="AMI21" s="0"/>
-      <c r="AMJ21" s="0"/>
-      <c r="AMK21" s="0"/>
-      <c r="AML21" s="0"/>
-      <c r="AMM21" s="0"/>
-    </row>
-    <row r="22" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>63</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+        <v>66</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
+      <c r="H22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -6142,77 +6049,92 @@
       <c r="AKI22" s="1"/>
       <c r="AKJ22" s="1"/>
       <c r="AKK22" s="1"/>
-      <c r="AKL22" s="0"/>
-      <c r="AKM22" s="0"/>
-      <c r="AKN22" s="0"/>
-      <c r="AKO22" s="0"/>
-      <c r="AKP22" s="0"/>
-      <c r="AKQ22" s="0"/>
-      <c r="AKR22" s="0"/>
-      <c r="AKS22" s="0"/>
-      <c r="AKT22" s="0"/>
-      <c r="AKU22" s="0"/>
-      <c r="AKV22" s="0"/>
-      <c r="AKW22" s="0"/>
-      <c r="AKX22" s="0"/>
-      <c r="AKY22" s="0"/>
-      <c r="AKZ22" s="0"/>
-      <c r="ALA22" s="0"/>
-      <c r="ALB22" s="0"/>
-      <c r="ALC22" s="0"/>
-      <c r="ALD22" s="0"/>
-      <c r="ALE22" s="0"/>
-      <c r="ALF22" s="0"/>
-      <c r="ALG22" s="0"/>
-      <c r="ALH22" s="0"/>
-      <c r="ALI22" s="0"/>
-      <c r="ALJ22" s="0"/>
-      <c r="ALK22" s="0"/>
-      <c r="ALL22" s="0"/>
-      <c r="ALM22" s="0"/>
-      <c r="ALN22" s="0"/>
-      <c r="ALO22" s="0"/>
-      <c r="ALP22" s="0"/>
-      <c r="ALQ22" s="0"/>
-      <c r="ALR22" s="0"/>
-      <c r="ALS22" s="0"/>
-      <c r="ALT22" s="0"/>
-      <c r="ALU22" s="0"/>
-      <c r="ALV22" s="0"/>
-      <c r="ALW22" s="0"/>
-      <c r="ALX22" s="0"/>
-      <c r="ALY22" s="0"/>
-      <c r="ALZ22" s="0"/>
-      <c r="AMA22" s="0"/>
-      <c r="AMB22" s="0"/>
-      <c r="AMC22" s="0"/>
-      <c r="AMD22" s="0"/>
-      <c r="AME22" s="0"/>
-      <c r="AMF22" s="0"/>
-      <c r="AMG22" s="0"/>
-      <c r="AMH22" s="0"/>
-      <c r="AMI22" s="0"/>
-      <c r="AMJ22" s="0"/>
-      <c r="AMK22" s="0"/>
-      <c r="AML22" s="0"/>
-      <c r="AMM22" s="0"/>
-    </row>
-    <row r="23" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AKL22" s="1"/>
+      <c r="AKM22" s="1"/>
+      <c r="AKN22" s="1"/>
+      <c r="AKO22" s="1"/>
+      <c r="AKP22" s="1"/>
+      <c r="AKQ22" s="1"/>
+      <c r="AKR22" s="1"/>
+      <c r="AKS22" s="1"/>
+      <c r="AKT22" s="1"/>
+      <c r="AKU22" s="1"/>
+      <c r="AKV22" s="1"/>
+      <c r="AKW22" s="1"/>
+      <c r="AKX22" s="1"/>
+      <c r="AKY22" s="1"/>
+      <c r="AKZ22" s="1"/>
+      <c r="ALA22" s="1"/>
+      <c r="ALB22" s="1"/>
+      <c r="ALC22" s="1"/>
+      <c r="ALD22" s="1"/>
+      <c r="ALE22" s="1"/>
+      <c r="ALF22" s="1"/>
+      <c r="ALG22" s="1"/>
+      <c r="ALH22" s="1"/>
+      <c r="ALI22" s="1"/>
+      <c r="ALJ22" s="1"/>
+      <c r="ALK22" s="1"/>
+      <c r="ALL22" s="1"/>
+      <c r="ALM22" s="1"/>
+      <c r="ALN22" s="1"/>
+      <c r="ALO22" s="1"/>
+      <c r="ALP22" s="1"/>
+      <c r="ALQ22" s="1"/>
+      <c r="ALR22" s="1"/>
+      <c r="ALS22" s="1"/>
+      <c r="ALT22" s="1"/>
+      <c r="ALU22" s="1"/>
+      <c r="ALV22" s="1"/>
+      <c r="ALW22" s="1"/>
+      <c r="ALX22" s="1"/>
+      <c r="ALY22" s="1"/>
+      <c r="ALZ22" s="1"/>
+      <c r="AMA22" s="1"/>
+      <c r="AMB22" s="1"/>
+      <c r="AMC22" s="1"/>
+      <c r="AMD22" s="1"/>
+      <c r="AME22" s="1"/>
+      <c r="AMF22" s="1"/>
+      <c r="AMG22" s="1"/>
+      <c r="AMH22" s="1"/>
+      <c r="AMI22" s="1"/>
+      <c r="AMJ22" s="1"/>
+      <c r="AMK22" s="1"/>
+      <c r="AML22" s="1"/>
+      <c r="AMM22" s="1"/>
+      <c r="AMN22" s="1"/>
+      <c r="AMO22" s="1"/>
+    </row>
+    <row r="23" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
+      <c r="H23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -7174,62 +7096,146 @@
       <c r="AKH23" s="2"/>
       <c r="AKI23" s="2"/>
       <c r="AKJ23" s="2"/>
-      <c r="AKL23" s="0"/>
-      <c r="AKM23" s="0"/>
-      <c r="AKN23" s="0"/>
-      <c r="AKO23" s="0"/>
-      <c r="AKP23" s="0"/>
-      <c r="AKQ23" s="0"/>
-      <c r="AKR23" s="0"/>
-      <c r="AKS23" s="0"/>
-      <c r="AKT23" s="0"/>
-      <c r="AKU23" s="0"/>
-      <c r="AKV23" s="0"/>
-      <c r="AKW23" s="0"/>
-      <c r="AKX23" s="0"/>
-      <c r="AKY23" s="0"/>
-      <c r="AKZ23" s="0"/>
-      <c r="ALA23" s="0"/>
-      <c r="ALB23" s="0"/>
-      <c r="ALC23" s="0"/>
-      <c r="ALD23" s="0"/>
-      <c r="ALE23" s="0"/>
-      <c r="ALF23" s="0"/>
-      <c r="ALG23" s="0"/>
-      <c r="ALH23" s="0"/>
-      <c r="ALI23" s="0"/>
-      <c r="ALJ23" s="0"/>
-      <c r="ALK23" s="0"/>
-      <c r="ALL23" s="0"/>
-      <c r="ALM23" s="0"/>
-      <c r="ALN23" s="0"/>
-      <c r="ALO23" s="0"/>
-      <c r="ALP23" s="0"/>
-      <c r="ALQ23" s="0"/>
-      <c r="ALR23" s="0"/>
-      <c r="ALS23" s="0"/>
-      <c r="ALT23" s="0"/>
-      <c r="ALU23" s="0"/>
-      <c r="ALV23" s="0"/>
-      <c r="ALW23" s="0"/>
-      <c r="ALX23" s="0"/>
-      <c r="ALY23" s="0"/>
-      <c r="ALZ23" s="0"/>
-      <c r="AMA23" s="0"/>
-      <c r="AMB23" s="0"/>
-      <c r="AMC23" s="0"/>
-      <c r="AMD23" s="0"/>
-      <c r="AME23" s="0"/>
-      <c r="AMF23" s="0"/>
-      <c r="AMG23" s="0"/>
-      <c r="AMH23" s="0"/>
-      <c r="AMI23" s="0"/>
-      <c r="AMJ23" s="0"/>
-      <c r="AMK23" s="0"/>
-      <c r="AML23" s="0"/>
-      <c r="AMM23" s="0"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="AKK23" s="2"/>
+      <c r="AKL23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <f aca="false">COUNTIF(C3:C23,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <f aca="false">COUNTIF(D3:D23,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <f aca="false">COUNTIF(E3:E23,"P")</f>
+        <v>21</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <f aca="false">COUNTIF(F3:F23,"P")</f>
+        <v>17</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1" t="n">
+        <f aca="false">COUNTIF(H3:H23,"P")</f>
+        <v>14</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="n">
+        <f aca="false">COUNTIF(J3:J23,"P")</f>
+        <v>18</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <f aca="false">COUNTIF(K3:K23,"P")</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <f aca="false">COUNTIF(C3:C23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <f aca="false">COUNTIF(D3:D23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <f aca="false">COUNTIF(E3:E23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <f aca="false">COUNTIF(F3:F23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <f aca="false">COUNTIF(H3:H23,"M")</f>
+        <v>1</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="n">
+        <f aca="false">COUNTIF(J3:J23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <f aca="false">COUNTIF(K3:K23,"M")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <f aca="false">COUNTIF(C3:C23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <f aca="false">COUNTIF(D3:D23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <f aca="false">COUNTIF(E3:E23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <f aca="false">COUNTIF(F3:F23,"T")</f>
+        <v>3</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <f aca="false">COUNTIF(H3:H23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="n">
+        <f aca="false">COUNTIF(J3:J23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <f aca="false">COUNTIF(K3:K23,"T")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <f aca="false">SUM(C24:C26)</f>
+        <v>21</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <f aca="false">SUM(D24:D26)</f>
+        <v>20</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <f aca="false">SUM(E24:E26)</f>
+        <v>21</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <f aca="false">SUM(F24:F26)</f>
+        <v>20</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <f aca="false">SUM(H24:H26)</f>
+        <v>15</v>
+      </c>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1" t="n">
+        <f aca="false">SUM(J24:J26)</f>
+        <v>18</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <f aca="false">SUM(K24:K26)</f>
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -7275,7 +7281,7 @@
         <v>45961</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7301,7 +7307,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0</v>
@@ -7322,7 +7328,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>3</v>
@@ -7337,7 +7343,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>4</v>
@@ -7355,7 +7361,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
@@ -7373,7 +7379,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0</v>
@@ -7391,7 +7397,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>3</v>
@@ -7409,7 +7415,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>4</v>
@@ -7430,7 +7436,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>3</v>
@@ -7445,7 +7451,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>3</v>
@@ -7460,7 +7466,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>3</v>
@@ -7481,7 +7487,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0</v>
@@ -7496,7 +7502,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>3</v>
@@ -7517,7 +7523,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>3</v>
@@ -7538,7 +7544,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>3</v>
@@ -7556,7 +7562,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>0</v>
@@ -7571,7 +7577,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>3</v>
@@ -7589,7 +7595,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>0</v>
@@ -7607,7 +7613,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>3</v>
@@ -7622,7 +7628,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>3</v>
@@ -7640,7 +7646,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>3</v>
@@ -7658,7 +7664,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>3</v>
@@ -7697,22 +7703,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7726,10 +7732,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -7743,16 +7749,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>10</v>
@@ -7766,16 +7772,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -7789,16 +7795,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -7812,7 +7818,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -7826,7 +7832,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -7840,16 +7846,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -7863,16 +7869,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -7891,13 +7897,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8</v>
@@ -7908,16 +7914,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>10</v>
@@ -7931,7 +7937,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>1</v>
@@ -7945,16 +7951,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -7968,16 +7974,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>7</v>
@@ -7991,16 +7997,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -8014,16 +8020,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -8037,16 +8043,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -8060,7 +8066,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -8074,16 +8080,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>10</v>
@@ -8097,16 +8103,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -8120,16 +8126,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -8143,16 +8149,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>10</v>
@@ -8166,16 +8172,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -8194,13 +8200,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -8208,13 +8214,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>7</v>
@@ -8225,16 +8231,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -8273,24 +8279,24 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>9</v>
@@ -8325,22 +8331,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8354,10 +8360,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -8371,16 +8377,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>10</v>
@@ -8394,16 +8400,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -8417,16 +8423,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -8440,7 +8446,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -8454,7 +8460,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -8468,16 +8474,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -8491,16 +8497,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -8514,16 +8520,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -8537,7 +8543,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -8551,16 +8557,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -8574,16 +8580,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -8597,7 +8603,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>1</v>
@@ -8611,16 +8617,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -8634,16 +8640,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>10</v>
@@ -8657,7 +8663,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -8671,16 +8677,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -8694,16 +8700,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>10</v>
@@ -8717,16 +8723,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -8740,16 +8746,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -8763,16 +8769,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>10</v>
@@ -8791,13 +8797,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -8805,13 +8811,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8</v>
@@ -8819,13 +8825,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>6</v>
@@ -8833,13 +8839,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>5</v>
@@ -8850,16 +8856,16 @@
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -8897,13 +8903,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8917,10 +8923,10 @@
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>7</v>
@@ -8931,16 +8937,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>10</v>
@@ -8951,16 +8957,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -8971,16 +8977,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -8991,7 +8997,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -9002,7 +9008,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -9013,16 +9019,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -9033,16 +9039,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -9053,16 +9059,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8</v>
@@ -9073,7 +9079,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -9084,16 +9090,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -9104,16 +9110,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -9124,16 +9130,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>7</v>
@@ -9144,16 +9150,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>7</v>
@@ -9164,16 +9170,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>7</v>
@@ -9184,7 +9190,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -9195,16 +9201,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>8</v>
@@ -9215,16 +9221,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>7</v>
@@ -9235,16 +9241,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -9255,16 +9261,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -9275,16 +9281,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -9295,16 +9301,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>8</v>
@@ -9339,22 +9345,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9373,16 +9379,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -9393,7 +9399,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -9404,16 +9410,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>9</v>
@@ -9424,7 +9430,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -9435,7 +9441,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -9446,16 +9452,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -9466,16 +9472,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -9486,16 +9492,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -9506,7 +9512,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -9517,16 +9523,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>7</v>
@@ -9537,16 +9543,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>7</v>
@@ -9557,7 +9563,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>1</v>
@@ -9568,16 +9574,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>7</v>
@@ -9588,16 +9594,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -9608,7 +9614,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -9619,7 +9625,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -9630,7 +9636,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>1</v>
@@ -9641,16 +9647,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>1</v>
@@ -9661,7 +9667,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>1</v>
@@ -9672,16 +9678,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>10</v>
@@ -9689,13 +9695,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>6</v>
@@ -9706,7 +9712,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>1</v>
@@ -9746,22 +9752,22 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9769,10 +9775,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>7</v>
@@ -9783,13 +9789,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>9</v>
@@ -9800,13 +9806,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>6</v>
@@ -9825,13 +9831,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>5</v>
@@ -9839,13 +9845,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>5</v>
@@ -9853,13 +9859,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>5</v>
@@ -9867,13 +9873,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>5</v>
@@ -9881,13 +9887,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>4</v>
@@ -9895,13 +9901,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>3</v>
@@ -9909,13 +9915,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>7</v>
@@ -9926,13 +9932,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>6</v>
@@ -9943,13 +9949,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>5</v>

--- a/inasistencias-6A-sistDeCtrolVirtual/Alumnos-6A-SistDeCtrolVirtual.xlsx
+++ b/inasistencias-6A-sistDeCtrolVirtual/Alumnos-6A-SistDeCtrolVirtual.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="58">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">ANDRADA BASCOPE</t>
   </si>
   <si>
+    <t xml:space="preserve">p</t>
+  </si>
+  <si>
     <t xml:space="preserve">APURIL</t>
   </si>
   <si>
     <t xml:space="preserve">AYBAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p</t>
   </si>
   <si>
     <t xml:space="preserve">bertola galizzi</t>
@@ -176,7 +176,16 @@
     <t xml:space="preserve">Valoracion</t>
   </si>
   <si>
-    <t xml:space="preserve">recursante</t>
+    <t xml:space="preserve">Grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reglamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valoreaion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corregir en planilla</t>
   </si>
   <si>
     <t xml:space="preserve">Calificación/10,00</t>
@@ -228,7 +237,7 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -239,6 +248,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBF00"/>
+        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
   </fills>
@@ -276,7 +291,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -321,6 +336,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,7 +361,50 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF006600"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FFCC0000"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -463,7 +537,7 @@
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
@@ -692,7 +766,7 @@
         <v>2</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>46231</v>
+        <v>46217</v>
       </c>
       <c r="AE2" s="3" t="n">
         <v>46238</v>
@@ -834,6 +908,15 @@
       <c r="AB3" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="AD3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -911,13 +994,22 @@
       <c r="AB4" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="AD4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
@@ -988,13 +1080,22 @@
       <c r="AB5" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="AD5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
@@ -1006,7 +1107,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>10</v>
@@ -1065,6 +1166,15 @@
       <c r="AB6" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="AD6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF6" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -1148,6 +1258,15 @@
       <c r="AB7" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AD7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -1229,6 +1348,15 @@
       <c r="AA8" s="1"/>
       <c r="AB8" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF8" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="AKR8" s="1"/>
       <c r="AKS8" s="1"/>
@@ -1369,6 +1497,15 @@
       <c r="AB9" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="AD9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF9" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -1446,6 +1583,15 @@
       <c r="AB10" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AD10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF10" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -1526,6 +1672,15 @@
       <c r="AC11" s="6" t="n">
         <v>0.5625</v>
       </c>
+      <c r="AD11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF11" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -1604,6 +1759,15 @@
       <c r="AA12" s="1"/>
       <c r="AB12" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="AD12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF12" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="AKR12" s="1"/>
       <c r="AKS12" s="1"/>
@@ -1741,6 +1905,15 @@
       <c r="AC13" s="6" t="n">
         <v>0.5625</v>
       </c>
+      <c r="AD13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF13" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -1818,6 +1991,15 @@
       <c r="AB14" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="AD14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF14" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -1901,6 +2083,15 @@
       </c>
       <c r="AC15" s="7" t="n">
         <v>0.5625</v>
+      </c>
+      <c r="AD15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF15" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="AKR15" s="1"/>
       <c r="AKS15" s="1"/>
@@ -2035,6 +2226,15 @@
       <c r="AB16" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="AD16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF16" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -2112,6 +2312,15 @@
       <c r="AB17" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="AD17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF17" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="18" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
@@ -2189,6 +2398,15 @@
       </c>
       <c r="AA18" s="1"/>
       <c r="AB18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="AKR18" s="8"/>
@@ -2326,6 +2544,15 @@
       <c r="AB19" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="AD19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF19" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="AKR19" s="1"/>
       <c r="AKS19" s="1"/>
       <c r="AKT19" s="1"/>
@@ -2418,7 +2645,7 @@
         <v>10</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>10</v>
@@ -2462,6 +2689,15 @@
       <c r="AB20" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="AD20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF20" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -2539,6 +2775,15 @@
       <c r="AB21" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="AD21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF21" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="22" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -2628,9 +2873,15 @@
         <v>10</v>
       </c>
       <c r="AC22" s="1"/>
-      <c r="AD22" s="1"/>
-      <c r="AE22" s="1"/>
-      <c r="AF22" s="1"/>
+      <c r="AD22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF22" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="AG22" s="1"/>
       <c r="AH22" s="1"/>
       <c r="AI22" s="1"/>
@@ -3715,9 +3966,15 @@
         <v>10</v>
       </c>
       <c r="AC23" s="2"/>
-      <c r="AD23" s="2"/>
-      <c r="AE23" s="2"/>
-      <c r="AF23" s="2"/>
+      <c r="AD23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF23" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="AG23" s="2"/>
       <c r="AH23" s="2"/>
       <c r="AI23" s="2"/>
@@ -4731,6 +4988,18 @@
         <f aca="false">COUNTIF(AB3:AB23,"P")</f>
         <v>14</v>
       </c>
+      <c r="AD24" s="1" t="n">
+        <f aca="false">COUNTIF(AD3:AD23,"P")</f>
+        <v>16</v>
+      </c>
+      <c r="AE24" s="1" t="n">
+        <f aca="false">COUNTIF(AE3:AE23,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="AF24" s="1" t="n">
+        <f aca="false">COUNTIF(AF3:AF23,"P")</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
@@ -4795,6 +5064,18 @@
       </c>
       <c r="AB25" s="1" t="n">
         <f aca="false">COUNTIF(AB3:AB23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="1" t="n">
+        <f aca="false">COUNTIF(AD3:AD23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="1" t="n">
+        <f aca="false">COUNTIF(AE3:AE23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AF25" s="1" t="n">
+        <f aca="false">COUNTIF(AF3:AF23,"M")</f>
         <v>0</v>
       </c>
     </row>
@@ -4863,6 +5144,18 @@
         <f aca="false">COUNTIF(AB3:AB23,"t")</f>
         <v>3</v>
       </c>
+      <c r="AD26" s="1" t="n">
+        <f aca="false">COUNTIF(AD3:AD23,"t")</f>
+        <v>0</v>
+      </c>
+      <c r="AE26" s="1" t="n">
+        <f aca="false">COUNTIF(AE3:AE23,"t")</f>
+        <v>0</v>
+      </c>
+      <c r="AF26" s="1" t="n">
+        <f aca="false">COUNTIF(AF3:AF23,"t")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
@@ -4928,6 +5221,18 @@
       <c r="AB27" s="1" t="n">
         <f aca="false">SUM(AB24:AB26)</f>
         <v>17</v>
+      </c>
+      <c r="AD27" s="1" t="n">
+        <f aca="false">SUM(AD24:AD26)</f>
+        <v>16</v>
+      </c>
+      <c r="AE27" s="1" t="n">
+        <f aca="false">SUM(AE24:AE26)</f>
+        <v>13</v>
+      </c>
+      <c r="AF27" s="1" t="n">
+        <f aca="false">SUM(AF24:AF26)</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5034,7 +5339,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>3</v>
@@ -5049,7 +5354,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>4</v>
@@ -5396,11 +5701,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:XFD22"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.94"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.55"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="6" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5423,28 +5731,46 @@
         <v>40</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>48</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5461,34 +5787,51 @@
         <v>46168</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="I2" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="J2" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="K2" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>9.67</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="M2" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C2,E2,G2,I2,K2,L2),0)</f>
-        <v>6</v>
-      </c>
-      <c r="N2" s="5" t="str">
-        <f aca="false">IF(M2&gt;6,"TEA",IF(M2&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+      <c r="N2" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C2,E2,H2,J2,L2,M2),0)</f>
+        <v>7</v>
+      </c>
+      <c r="O2" s="5" t="str">
+        <f aca="false">IF(N2&gt;6,"TEA",IF(N2&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N2,Q2),0)</f>
+        <v>7</v>
+      </c>
+      <c r="S2" s="5" t="str">
+        <f aca="false">IF(R2&gt;6,"TEA",IF(R2&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5503,33 +5846,50 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>46168</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="L3" s="2" t="n">
         <v>9.33</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="M3" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="M3" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C3,E3,G3,I3,K3,L3),0)</f>
-        <v>7</v>
-      </c>
-      <c r="N3" s="5" t="str">
-        <f aca="false">IF(M3&gt;6,"TEA",IF(M3&gt;3,"TEP","TED"))</f>
+      <c r="N3" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C3,E3,H3,J3,L3,M3),0)</f>
+        <v>8</v>
+      </c>
+      <c r="O3" s="5" t="str">
+        <f aca="false">IF(N3&gt;6,"TEA",IF(N3&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N3,Q3),0)</f>
+        <v>9</v>
+      </c>
+      <c r="S3" s="5" t="str">
+        <f aca="false">IF(R3&gt;6,"TEA",IF(R3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -5538,7 +5898,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>6</v>
@@ -5547,32 +5907,51 @@
         <v>46168</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="F4" s="4" t="n">
         <v>46168</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="L4" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L4" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C4,E4,G4,I4,K4,L4),0)</f>
-        <v>6</v>
-      </c>
-      <c r="N4" s="5" t="str">
-        <f aca="false">IF(M4&gt;6,"TEA",IF(M4&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+      <c r="M4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C4,E4,H4,J4,L4,M4),0)</f>
+        <v>8</v>
+      </c>
+      <c r="O4" s="5" t="str">
+        <f aca="false">IF(N4&gt;6,"TEA",IF(N4&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N4,Q4),0)</f>
+        <v>8</v>
+      </c>
+      <c r="S4" s="5" t="str">
+        <f aca="false">IF(R4&gt;6,"TEA",IF(R4&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5580,7 +5959,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>8</v>
@@ -5590,26 +5969,41 @@
         <v>10</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" s="2"/>
       <c r="L5" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M5" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C5,E5,G5,I5,K5,L5),0)</f>
-        <v>10</v>
-      </c>
-      <c r="N5" s="5" t="str">
-        <f aca="false">IF(M5&gt;6,"TEA",IF(M5&gt;3,"TEP","TED"))</f>
+      <c r="M5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C5,E5,H5,J5,L5,M5),0)</f>
+        <v>10</v>
+      </c>
+      <c r="O5" s="5" t="str">
+        <f aca="false">IF(N5&gt;6,"TEA",IF(N5&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N5,Q5),0)</f>
+        <v>10</v>
+      </c>
+      <c r="S5" s="5" t="str">
+        <f aca="false">IF(R5&gt;6,"TEA",IF(R5&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -5628,28 +6022,43 @@
         <v>10</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="2"/>
+      <c r="H6" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="K6" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>9.67</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M6" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C6,E6,G6,I6,K6,L6),0)</f>
+      <c r="N6" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C6,E6,H6,J6,L6,M6),0)</f>
         <v>7</v>
       </c>
-      <c r="N6" s="5" t="str">
-        <f aca="false">IF(M6&gt;6,"TEA",IF(M6&gt;3,"TEP","TED"))</f>
+      <c r="O6" s="5" t="str">
+        <f aca="false">IF(N6&gt;6,"TEA",IF(N6&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N6,Q6),0)</f>
+        <v>9</v>
+      </c>
+      <c r="S6" s="5" t="str">
+        <f aca="false">IF(R6&gt;6,"TEA",IF(R6&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -5668,26 +6077,41 @@
         <v>10</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="2"/>
+      <c r="H7" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="2"/>
+      <c r="J7" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="2"/>
+      <c r="L7" s="2" t="n">
         <v>9.67</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="M7" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="M7" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C7,E7,G7,I7,K7,L7),0)</f>
+      <c r="N7" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C7,E7,H7,J7,L7,M7),0)</f>
         <v>9</v>
       </c>
-      <c r="N7" s="5" t="str">
-        <f aca="false">IF(M7&gt;6,"TEA",IF(M7&gt;3,"TEP","TED"))</f>
+      <c r="O7" s="5" t="str">
+        <f aca="false">IF(N7&gt;6,"TEA",IF(N7&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N7,Q7),0)</f>
+        <v>10</v>
+      </c>
+      <c r="S7" s="5" t="str">
+        <f aca="false">IF(R7&gt;6,"TEA",IF(R7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -5699,34 +6123,57 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>46217</v>
+      </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>46217</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>46217</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>46217</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M8" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C8,E8,G8,I8,K8,L8),0)</f>
-        <v>4</v>
-      </c>
-      <c r="N8" s="5" t="str">
-        <f aca="false">IF(M8&gt;6,"TEA",IF(M8&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+      <c r="M8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C8,E8,H8,J8,L8,M8),0)</f>
+        <v>8</v>
+      </c>
+      <c r="O8" s="5" t="str">
+        <f aca="false">IF(N8&gt;6,"TEA",IF(N8&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R8" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N8,Q8),0)</f>
+        <v>9</v>
+      </c>
+      <c r="S8" s="5" t="str">
+        <f aca="false">IF(R8&gt;6,"TEA",IF(R8&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5744,26 +6191,41 @@
         <v>10</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2" t="n">
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="K9" s="2"/>
       <c r="L9" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M9" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C9,E9,G9,I9,K9,L9),0)</f>
-        <v>10</v>
-      </c>
-      <c r="N9" s="5" t="str">
-        <f aca="false">IF(M9&gt;6,"TEA",IF(M9&gt;3,"TEP","TED"))</f>
+      <c r="M9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C9,E9,H9,J9,L9,M9),0)</f>
+        <v>10</v>
+      </c>
+      <c r="O9" s="5" t="str">
+        <f aca="false">IF(N9&gt;6,"TEA",IF(N9&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N9,Q9),0)</f>
+        <v>10</v>
+      </c>
+      <c r="S9" s="5" t="str">
+        <f aca="false">IF(R9&gt;6,"TEA",IF(R9&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -5781,29 +6243,44 @@
       <c r="E10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="2"/>
+      <c r="G10" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2" t="n">
+      <c r="I10" s="2"/>
+      <c r="J10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2" t="n">
         <v>9.33</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="M10" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="M10" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C10,E10,G10,I10,K10,L10),0)</f>
+      <c r="N10" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C10,E10,H10,J10,L10,M10),0)</f>
         <v>9</v>
       </c>
-      <c r="N10" s="5" t="str">
-        <f aca="false">IF(M10&gt;6,"TEA",IF(M10&gt;3,"TEP","TED"))</f>
+      <c r="O10" s="5" t="str">
+        <f aca="false">IF(N10&gt;6,"TEA",IF(N10&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N10,Q10),0)</f>
+        <v>10</v>
+      </c>
+      <c r="S10" s="5" t="str">
+        <f aca="false">IF(R10&gt;6,"TEA",IF(R10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -5815,34 +6292,55 @@
         <v>22</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>46217</v>
+      </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>46217</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>46217</v>
       </c>
       <c r="L11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="M11" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C11,E11,G11,I11,K11,L11),0)</f>
-        <v>5</v>
-      </c>
-      <c r="N11" s="5" t="str">
-        <f aca="false">IF(M11&gt;6,"TEA",IF(M11&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+      <c r="N11" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C11,E11,H11,J11,L11,M11),0)</f>
+        <v>8</v>
+      </c>
+      <c r="O11" s="5" t="str">
+        <f aca="false">IF(N11&gt;6,"TEA",IF(N11&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N11,Q11),0)</f>
+        <v>9</v>
+      </c>
+      <c r="S11" s="5" t="str">
+        <f aca="false">IF(R11&gt;6,"TEA",IF(R11&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5860,26 +6358,41 @@
         <v>10</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="2"/>
+      <c r="H12" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="2"/>
+      <c r="J12" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="2"/>
+      <c r="L12" s="2" t="n">
         <v>9.33</v>
       </c>
-      <c r="L12" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C12,E12,G12,I12,K12,L12),0)</f>
+      <c r="M12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C12,E12,H12,J12,L12,M12),0)</f>
         <v>9</v>
       </c>
-      <c r="N12" s="5" t="str">
-        <f aca="false">IF(M12&gt;6,"TEA",IF(M12&gt;3,"TEP","TED"))</f>
+      <c r="O12" s="5" t="str">
+        <f aca="false">IF(N12&gt;6,"TEA",IF(N12&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N12,Q12),0)</f>
+        <v>10</v>
+      </c>
+      <c r="S12" s="5" t="str">
+        <f aca="false">IF(R12&gt;6,"TEA",IF(R12&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -5898,26 +6411,41 @@
         <v>10</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="2"/>
+      <c r="H13" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M13" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="M13" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C13,E13,G13,I13,K13,L13),0)</f>
-        <v>10</v>
-      </c>
-      <c r="N13" s="5" t="str">
-        <f aca="false">IF(M13&gt;6,"TEA",IF(M13&gt;3,"TEP","TED"))</f>
+      <c r="N13" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C13,E13,H13,J13,L13,M13),0)</f>
+        <v>10</v>
+      </c>
+      <c r="O13" s="5" t="str">
+        <f aca="false">IF(N13&gt;6,"TEA",IF(N13&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N13,Q13),0)</f>
+        <v>10</v>
+      </c>
+      <c r="S13" s="5" t="str">
+        <f aca="false">IF(R13&gt;6,"TEA",IF(R13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -5936,29 +6464,44 @@
         <v>1</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2" t="n">
+      <c r="G14" s="2"/>
+      <c r="H14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="K14" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="L14" s="2" t="n">
         <v>9.67</v>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="M14" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="M14" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C14,E14,G14,I14,K14,L14),0)</f>
+      <c r="N14" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C14,E14,H14,J14,L14,M14),0)</f>
         <v>5</v>
       </c>
-      <c r="N14" s="5" t="str">
-        <f aca="false">IF(M14&gt;6,"TEA",IF(M14&gt;3,"TEP","TED"))</f>
+      <c r="O14" s="5" t="str">
+        <f aca="false">IF(N14&gt;6,"TEA",IF(N14&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N14,Q14),0)</f>
+        <v>3</v>
+      </c>
+      <c r="S14" s="5" t="str">
+        <f aca="false">IF(R14&gt;6,"TEA",IF(R14&gt;3,"TEP","TED"))</f>
+        <v>TED</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5975,33 +6518,48 @@
       <c r="E15" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="2"/>
+      <c r="G15" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="I15" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="J15" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="K15" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="K15" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="L15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="M15" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C15,E15,G15,I15,K15,L15),0)</f>
+      <c r="M15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C15,E15,H15,J15,L15,M15),0)</f>
         <v>9</v>
       </c>
-      <c r="N15" s="5" t="str">
-        <f aca="false">IF(M15&gt;6,"TEA",IF(M15&gt;3,"TEP","TED"))</f>
+      <c r="O15" s="5" t="str">
+        <f aca="false">IF(N15&gt;6,"TEA",IF(N15&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N15,Q15),0)</f>
+        <v>10</v>
+      </c>
+      <c r="S15" s="5" t="str">
+        <f aca="false">IF(R15&gt;6,"TEA",IF(R15&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -6021,33 +6579,48 @@
       <c r="E16" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="2"/>
+      <c r="G16" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="I16" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="K16" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="L16" s="2" t="n">
         <v>9.33</v>
       </c>
-      <c r="L16" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C16,E16,G16,I16,K16,L16),0)</f>
+      <c r="M16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C16,E16,H16,J16,L16,M16),0)</f>
         <v>8</v>
       </c>
-      <c r="N16" s="5" t="str">
-        <f aca="false">IF(M16&gt;6,"TEA",IF(M16&gt;3,"TEP","TED"))</f>
+      <c r="O16" s="5" t="str">
+        <f aca="false">IF(N16&gt;6,"TEA",IF(N16&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R16" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N16,Q16),0)</f>
+        <v>9</v>
+      </c>
+      <c r="S16" s="5" t="str">
+        <f aca="false">IF(R16&gt;6,"TEA",IF(R16&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -6059,38 +6632,53 @@
         <v>28</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="8"/>
+        <v>7</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>46217</v>
+      </c>
       <c r="E17" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="8"/>
-      <c r="G17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="8"/>
       <c r="L17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="M17" s="10" t="n">
-        <f aca="false">ROUND(AVERAGE(C17,E17,G17,I17,K17,L17),0)</f>
+      <c r="N17" s="10" t="n">
+        <f aca="false">ROUND(AVERAGE(C17,E17,H17,J17,L17,M17),0)</f>
+        <v>3</v>
+      </c>
+      <c r="O17" s="5" t="str">
+        <f aca="false">IF(N17&gt;6,"TEA",IF(N17&gt;3,"TEP","TED"))</f>
+        <v>TED</v>
+      </c>
+      <c r="P17" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N17,Q17),0)</f>
         <v>2</v>
       </c>
-      <c r="N17" s="5" t="str">
-        <f aca="false">IF(M17&gt;6,"TEA",IF(M17&gt;3,"TEP","TED"))</f>
+      <c r="S17" s="5" t="str">
+        <f aca="false">IF(R17&gt;6,"TEA",IF(R17&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="O17" s="9" t="s">
-        <v>49</v>
-      </c>
+      <c r="XFD17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
@@ -6107,27 +6695,42 @@
         <v>1</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2" t="n">
+      <c r="G18" s="2"/>
+      <c r="H18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2" t="n">
         <v>9.33</v>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="M18" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="M18" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C18,E18,G18,I18,K18,L18),0)</f>
+      <c r="N18" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C18,E18,H18,J18,L18,M18),0)</f>
         <v>4</v>
       </c>
-      <c r="N18" s="5" t="str">
-        <f aca="false">IF(M18&gt;6,"TEA",IF(M18&gt;3,"TEP","TED"))</f>
+      <c r="O18" s="5" t="str">
+        <f aca="false">IF(N18&gt;6,"TEA",IF(N18&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N18,Q18),0)</f>
+        <v>7</v>
+      </c>
+      <c r="S18" s="5" t="str">
+        <f aca="false">IF(R18&gt;6,"TEA",IF(R18&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6146,33 +6749,48 @@
       <c r="E19" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="2"/>
+      <c r="G19" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="H19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="I19" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="J19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="K19" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="K19" s="2" t="n">
+      <c r="L19" s="2" t="n">
         <v>9.33</v>
       </c>
-      <c r="L19" s="2" t="n">
+      <c r="M19" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="M19" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C19,E19,G19,I19,K19,L19),0)</f>
+      <c r="N19" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C19,E19,H19,J19,L19,M19),0)</f>
         <v>8</v>
       </c>
-      <c r="N19" s="5" t="str">
-        <f aca="false">IF(M19&gt;6,"TEA",IF(M19&gt;3,"TEP","TED"))</f>
+      <c r="O19" s="5" t="str">
+        <f aca="false">IF(N19&gt;6,"TEA",IF(N19&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N19,Q19),0)</f>
+        <v>9</v>
+      </c>
+      <c r="S19" s="5" t="str">
+        <f aca="false">IF(R19&gt;6,"TEA",IF(R19&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -6190,33 +6808,50 @@
         <v>46168</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>46168</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="I20" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="J20" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="K20" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="L20" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L20" s="2" t="n">
+      <c r="M20" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="M20" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C20,E20,G20,I20,K20,L20),0)</f>
+      <c r="N20" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C20,E20,H20,J20,L20,M20),0)</f>
         <v>7</v>
       </c>
-      <c r="N20" s="5" t="str">
-        <f aca="false">IF(M20&gt;6,"TEA",IF(M20&gt;3,"TEP","TED"))</f>
+      <c r="O20" s="5" t="str">
+        <f aca="false">IF(N20&gt;6,"TEA",IF(N20&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N20,Q20),0)</f>
+        <v>7</v>
+      </c>
+      <c r="S20" s="5" t="str">
+        <f aca="false">IF(R20&gt;6,"TEA",IF(R20&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -6236,76 +6871,114 @@
       <c r="E21" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="2"/>
+      <c r="G21" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="H21" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="I21" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2" t="n">
+      <c r="J21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2" t="n">
         <v>8.33</v>
       </c>
-      <c r="L21" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M21" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C21,E21,G21,I21,K21,L21),0)</f>
+      <c r="M21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(C21,E21,H21,J21,L21,M21),0)</f>
         <v>9</v>
       </c>
-      <c r="N21" s="5" t="str">
-        <f aca="false">IF(M21&gt;6,"TEA",IF(M21&gt;3,"TEP","TED"))</f>
+      <c r="O21" s="5" t="str">
+        <f aca="false">IF(N21&gt;6,"TEA",IF(N21&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
+      <c r="P21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="R21" s="5" t="n">
+        <f aca="false">ROUND(AVERAGE(N21,Q21),0)</f>
+        <v>10</v>
+      </c>
+      <c r="S21" s="5" t="str">
+        <f aca="false">IF(R21&gt;6,"TEA",IF(R21&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+    </row>
+    <row r="22" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2" t="n">
+      <c r="C22" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>46126</v>
+      </c>
+      <c r="E22" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J22" s="3" t="n">
-        <v>46168</v>
-      </c>
-      <c r="K22" s="2" t="n">
+      <c r="F22" s="13" t="n">
+        <v>46126</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" s="13" t="n">
+        <v>46126</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>46126</v>
+      </c>
+      <c r="L22" s="12" t="n">
         <v>9.33</v>
       </c>
-      <c r="L22" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <f aca="false">ROUND(AVERAGE(C22,E22,G22,I22,K22,L22),0)</f>
-        <v>5</v>
-      </c>
-      <c r="N22" s="5" t="str">
-        <f aca="false">IF(M22&gt;6,"TEA",IF(M22&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+      <c r="M22" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <f aca="false">ROUND(AVERAGE(C22,E22,H22,J22,L22,M22),0)</f>
+        <v>8</v>
+      </c>
+      <c r="O22" s="14" t="str">
+        <f aca="false">IF(N22&gt;6,"TEA",IF(N22&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="R22" s="14" t="n">
+        <f aca="false">ROUND(AVERAGE(N22,Q22),0)</f>
+        <v>8</v>
+      </c>
+      <c r="S22" s="14" t="str">
+        <f aca="false">IF(R22&gt;6,"TEA",IF(R22&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="T22" s="12" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M2:N22">
+  <conditionalFormatting sqref="N2:O22 S2:S22">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>7</formula>
     </cfRule>
@@ -6326,7 +6999,7 @@
       <formula>"TED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:L22">
+  <conditionalFormatting sqref="C1:M22">
     <cfRule type="cellIs" priority="8" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>6</formula>
     </cfRule>
@@ -6335,6 +7008,30 @@
       <formula>6</formula>
     </cfRule>
     <cfRule type="cellIs" priority="10" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R22">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>4</formula>
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q22">
+    <cfRule type="cellIs" priority="14" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>4</formula>
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6372,16 +7069,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6420,7 +7117,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
@@ -6434,10 +7131,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>8</v>
@@ -6789,7 +7486,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6819,7 +7516,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
@@ -6830,10 +7527,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>10</v>
@@ -7086,16 +7783,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7131,7 +7828,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
@@ -7145,10 +7842,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>9</v>
@@ -7490,7 +8187,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F29" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G29" s="1" t="n">
         <f aca="false">COUNTIF(G2:G28,"&gt;0")</f>
@@ -7532,16 +8229,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7577,7 +8274,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
@@ -7591,10 +8288,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>10</v>
@@ -7927,7 +8624,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7963,10 +8660,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>9</v>
@@ -7977,10 +8674,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>10</v>
@@ -8223,7 +8920,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/inasistencias-6A-sistDeCtrolVirtual/Alumnos-6A-SistDeCtrolVirtual.xlsx
+++ b/inasistencias-6A-sistDeCtrolVirtual/Alumnos-6A-SistDeCtrolVirtual.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="asistencia" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="64">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -179,10 +179,28 @@
     <t xml:space="preserve">Grupo</t>
   </si>
   <si>
-    <t xml:space="preserve">reglamento</t>
+    <t xml:space="preserve">9-reglamento</t>
   </si>
   <si>
     <t xml:space="preserve">valoreaion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grupos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-codigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11-java Script</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-BaseDatosJuevos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13-InstrumenData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">falta el liink al repositorio</t>
   </si>
   <si>
     <t xml:space="preserve">corregir en planilla</t>
@@ -213,7 +231,7 @@
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="hh:mm:ss"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -235,6 +253,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -291,7 +317,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -332,6 +358,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -361,7 +395,50 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF006600"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FFCC0000"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -666,14 +743,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XDJ27"/>
+  <dimension ref="A1:XDL27"/>
   <sheetFormatPr defaultColWidth="9.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="23" min="3" style="1" width="9.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="980" min="980" style="1" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16338" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="32" min="3" style="1" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="982" min="982" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16340" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -775,60 +852,64 @@
         <v>46245</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>46252</v>
-      </c>
-      <c r="AH2" s="3" t="n">
         <v>46259</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46266</v>
       </c>
-      <c r="AJ2" s="3" t="n">
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3" t="n">
         <v>46273</v>
       </c>
-      <c r="AK2" s="3" t="n">
+      <c r="AL2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM2" s="3" t="n">
         <v>46280</v>
       </c>
-      <c r="AL2" s="3" t="n">
+      <c r="AN2" s="3" t="n">
         <v>46287</v>
       </c>
-      <c r="AM2" s="3" t="n">
+      <c r="AO2" s="3" t="n">
         <v>46294</v>
       </c>
-      <c r="AN2" s="3" t="n">
+      <c r="AP2" s="3" t="n">
         <v>46301</v>
       </c>
-      <c r="AO2" s="3" t="n">
+      <c r="AQ2" s="3" t="n">
         <v>46308</v>
       </c>
-      <c r="AP2" s="3" t="n">
+      <c r="AR2" s="3" t="n">
         <v>46315</v>
       </c>
-      <c r="AQ2" s="3" t="n">
+      <c r="AS2" s="3" t="n">
         <v>46322</v>
       </c>
-      <c r="AR2" s="3" t="n">
+      <c r="AT2" s="3" t="n">
         <v>46329</v>
       </c>
-      <c r="AS2" s="3" t="n">
+      <c r="AU2" s="3" t="n">
         <v>46336</v>
       </c>
-      <c r="AT2" s="3" t="n">
+      <c r="AV2" s="3" t="n">
         <v>46343</v>
       </c>
-      <c r="AU2" s="3" t="n">
+      <c r="AW2" s="3" t="n">
         <v>46350</v>
       </c>
-      <c r="AV2" s="3" t="n">
+      <c r="AX2" s="3" t="n">
         <v>46357</v>
       </c>
-      <c r="AW2" s="3" t="n">
+      <c r="AY2" s="3" t="n">
         <v>46364</v>
       </c>
-      <c r="AX2" s="3" t="n">
+      <c r="AZ2" s="3" t="n">
         <v>46371</v>
       </c>
-      <c r="AY2" s="3" t="n">
+      <c r="BA2" s="3" t="n">
         <v>46378</v>
       </c>
     </row>
@@ -917,6 +998,33 @@
       <c r="AF3" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AG3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ3" s="6" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="AK3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL3" s="6" t="n">
+        <v>0.555555555555556</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -1003,6 +1111,27 @@
       <c r="AF4" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AG4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -1089,6 +1218,33 @@
       <c r="AF5" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AG5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ5" s="6" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="AK5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL5" s="6" t="n">
+        <v>0.555555555555556</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP5" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -1175,6 +1331,27 @@
       <c r="AF6" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AG6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP6" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -1267,6 +1444,27 @@
       <c r="AF7" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AG7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP7" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -1358,8 +1556,27 @@
       <c r="AF8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AKR8" s="1"/>
-      <c r="AKS8" s="1"/>
+      <c r="AG8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP8" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="AKT8" s="1"/>
       <c r="AKU8" s="1"/>
       <c r="AKV8" s="1"/>
@@ -1413,7 +1630,9 @@
       <c r="AMR8" s="1"/>
       <c r="AMS8" s="1"/>
       <c r="AMT8" s="1"/>
-      <c r="XDJ8" s="1"/>
+      <c r="AMU8" s="1"/>
+      <c r="AMV8" s="1"/>
+      <c r="XDL8" s="1"/>
     </row>
     <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -1506,6 +1725,27 @@
       <c r="AF9" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AG9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP9" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -1592,6 +1832,27 @@
       <c r="AF10" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AG10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP10" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -1681,6 +1942,33 @@
       <c r="AF11" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AG11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ11" s="6" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="AK11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL11" s="6" t="n">
+        <v>0.555555555555556</v>
+      </c>
+      <c r="AM11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP11" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -1769,8 +2057,27 @@
       <c r="AF12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AKR12" s="1"/>
-      <c r="AKS12" s="1"/>
+      <c r="AG12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP12" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="AKT12" s="1"/>
       <c r="AKU12" s="1"/>
       <c r="AKV12" s="1"/>
@@ -1824,7 +2131,9 @@
       <c r="AMR12" s="1"/>
       <c r="AMS12" s="1"/>
       <c r="AMT12" s="1"/>
-      <c r="XDJ12" s="1"/>
+      <c r="AMU12" s="1"/>
+      <c r="AMV12" s="1"/>
+      <c r="XDL12" s="1"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -1914,6 +2223,27 @@
       <c r="AF13" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AG13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP13" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -2000,6 +2330,27 @@
       <c r="AF14" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AG14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP14" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -2093,8 +2444,27 @@
       <c r="AF15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AKR15" s="1"/>
-      <c r="AKS15" s="1"/>
+      <c r="AG15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AK15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP15" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="AKT15" s="1"/>
       <c r="AKU15" s="1"/>
       <c r="AKV15" s="1"/>
@@ -2148,7 +2518,9 @@
       <c r="AMR15" s="1"/>
       <c r="AMS15" s="1"/>
       <c r="AMT15" s="1"/>
-      <c r="XDJ15" s="1"/>
+      <c r="AMU15" s="1"/>
+      <c r="AMV15" s="1"/>
+      <c r="XDL15" s="1"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
@@ -2235,6 +2607,27 @@
       <c r="AF16" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AG16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP16" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -2321,6 +2714,36 @@
       <c r="AF17" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AG17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH17" s="6" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AI17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ17" s="6" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="AK17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL17" s="6" t="n">
+        <v>0.555555555555556</v>
+      </c>
+      <c r="AM17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP17" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="18" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
@@ -2409,8 +2832,27 @@
       <c r="AF18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AKR18" s="8"/>
-      <c r="AKS18" s="8"/>
+      <c r="AG18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AK18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP18" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="AKT18" s="8"/>
       <c r="AKU18" s="8"/>
       <c r="AKV18" s="8"/>
@@ -2464,7 +2906,9 @@
       <c r="AMR18" s="8"/>
       <c r="AMS18" s="8"/>
       <c r="AMT18" s="8"/>
-      <c r="XDJ18" s="1"/>
+      <c r="AMU18" s="8"/>
+      <c r="AMV18" s="8"/>
+      <c r="XDL18" s="1"/>
     </row>
     <row r="19" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
@@ -2553,8 +2997,27 @@
       <c r="AF19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AKR19" s="1"/>
-      <c r="AKS19" s="1"/>
+      <c r="AG19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP19" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="AKT19" s="1"/>
       <c r="AKU19" s="1"/>
       <c r="AKV19" s="1"/>
@@ -2608,7 +3071,9 @@
       <c r="AMR19" s="1"/>
       <c r="AMS19" s="1"/>
       <c r="AMT19" s="1"/>
-      <c r="XDJ19" s="1"/>
+      <c r="AMU19" s="1"/>
+      <c r="AMV19" s="1"/>
+      <c r="XDL19" s="1"/>
     </row>
     <row r="20" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
@@ -2698,6 +3163,27 @@
       <c r="AF20" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="AG20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AK20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP20" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -2784,6 +3270,33 @@
       <c r="AF21" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AG21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ21" s="6" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="AK21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL21" s="6" t="n">
+        <v>0.555555555555556</v>
+      </c>
+      <c r="AM21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP21" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="22" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
@@ -2882,16 +3395,34 @@
       <c r="AF22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AG22" s="1"/>
-      <c r="AH22" s="1"/>
-      <c r="AI22" s="1"/>
+      <c r="AG22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH22" s="6" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="AI22" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="AJ22" s="1"/>
-      <c r="AK22" s="1"/>
-      <c r="AL22" s="1"/>
-      <c r="AM22" s="1"/>
-      <c r="AN22" s="1"/>
-      <c r="AO22" s="1"/>
-      <c r="AP22" s="1"/>
+      <c r="AK22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL22" s="6" t="n">
+        <v>0.555555555555556</v>
+      </c>
+      <c r="AM22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP22" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="AQ22" s="1"/>
       <c r="AR22" s="1"/>
       <c r="AS22" s="1"/>
@@ -3884,7 +4415,9 @@
       <c r="AMR22" s="1"/>
       <c r="AMS22" s="1"/>
       <c r="AMT22" s="1"/>
-      <c r="XDJ22" s="1"/>
+      <c r="AMU22" s="1"/>
+      <c r="AMV22" s="1"/>
+      <c r="XDL22" s="1"/>
     </row>
     <row r="23" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
@@ -3975,16 +4508,32 @@
       <c r="AF23" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AG23" s="2"/>
+      <c r="AG23" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="AH23" s="2"/>
-      <c r="AI23" s="2"/>
+      <c r="AI23" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="AJ23" s="2"/>
-      <c r="AK23" s="2"/>
-      <c r="AL23" s="2"/>
-      <c r="AM23" s="2"/>
-      <c r="AN23" s="2"/>
-      <c r="AO23" s="2"/>
-      <c r="AP23" s="2"/>
+      <c r="AK23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL23" s="7" t="n">
+        <v>0.555555555555556</v>
+      </c>
+      <c r="AM23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP23" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="AQ23" s="2"/>
       <c r="AR23" s="2"/>
       <c r="AS23" s="2"/>
@@ -4922,6 +5471,8 @@
       <c r="AKO23" s="2"/>
       <c r="AKP23" s="2"/>
       <c r="AKQ23" s="2"/>
+      <c r="AKR23" s="2"/>
+      <c r="AKS23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
@@ -4979,7 +5530,6 @@
         <f aca="false">COUNTIF(X3:X23,"P")</f>
         <v>15</v>
       </c>
-      <c r="Y24" s="1"/>
       <c r="Z24" s="1" t="n">
         <f aca="false">COUNTIF(Z3:Z23,"P")</f>
         <v>16</v>
@@ -5000,6 +5550,37 @@
         <f aca="false">COUNTIF(AF3:AF23,"P")</f>
         <v>2</v>
       </c>
+      <c r="AG24" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG23,"P")</f>
+        <v>14</v>
+      </c>
+      <c r="AH24" s="1"/>
+      <c r="AI24" s="1" t="n">
+        <f aca="false">COUNTIF(AI3:AI23,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="AJ24" s="1"/>
+      <c r="AK24" s="1" t="n">
+        <f aca="false">COUNTIF(AK3:AK23,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="AL24" s="1"/>
+      <c r="AM24" s="1" t="n">
+        <f aca="false">COUNTIF(AM3:AM23,"P")</f>
+        <v>15</v>
+      </c>
+      <c r="AN24" s="1" t="n">
+        <f aca="false">COUNTIF(AN3:AN23,"P")</f>
+        <v>16</v>
+      </c>
+      <c r="AO24" s="1" t="n">
+        <f aca="false">COUNTIF(AO3:AO23,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="AP24" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP23,"P")</f>
+        <v>19</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
@@ -5057,7 +5638,6 @@
         <f aca="false">COUNTIF(X3:X23,"M")</f>
         <v>0</v>
       </c>
-      <c r="Y25" s="1"/>
       <c r="Z25" s="1" t="n">
         <f aca="false">COUNTIF(Z3:Z23,"M")</f>
         <v>0</v>
@@ -5076,6 +5656,37 @@
       </c>
       <c r="AF25" s="1" t="n">
         <f aca="false">COUNTIF(AF3:AF23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AG25" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="1"/>
+      <c r="AI25" s="1" t="n">
+        <f aca="false">COUNTIF(AI3:AI23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="1"/>
+      <c r="AK25" s="1" t="n">
+        <f aca="false">COUNTIF(AK3:AK23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL25" s="1"/>
+      <c r="AM25" s="1" t="n">
+        <f aca="false">COUNTIF(AM3:AM23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AN25" s="1" t="n">
+        <f aca="false">COUNTIF(AN3:AN23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AO25" s="1" t="n">
+        <f aca="false">COUNTIF(AO3:AO23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AP25" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP23,"M")</f>
         <v>0</v>
       </c>
     </row>
@@ -5135,7 +5746,6 @@
         <f aca="false">COUNTIF(X3:X23,"t")</f>
         <v>2</v>
       </c>
-      <c r="Y26" s="1"/>
       <c r="Z26" s="1" t="n">
         <f aca="false">COUNTIF(Z3:Z23,"t")</f>
         <v>3</v>
@@ -5156,6 +5766,37 @@
         <f aca="false">COUNTIF(AF3:AF23,"t")</f>
         <v>0</v>
       </c>
+      <c r="AG26" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG23,"t")</f>
+        <v>2</v>
+      </c>
+      <c r="AH26" s="1"/>
+      <c r="AI26" s="1" t="n">
+        <f aca="false">COUNTIF(AI3:AI23,"t")</f>
+        <v>5</v>
+      </c>
+      <c r="AJ26" s="1"/>
+      <c r="AK26" s="1" t="n">
+        <f aca="false">COUNTIF(AK3:AK23,"t")</f>
+        <v>7</v>
+      </c>
+      <c r="AL26" s="1"/>
+      <c r="AM26" s="1" t="n">
+        <f aca="false">COUNTIF(AM3:AM23,"t")</f>
+        <v>0</v>
+      </c>
+      <c r="AN26" s="1" t="n">
+        <f aca="false">COUNTIF(AN3:AN23,"t")</f>
+        <v>0</v>
+      </c>
+      <c r="AO26" s="1" t="n">
+        <f aca="false">COUNTIF(AO3:AO23,"t")</f>
+        <v>0</v>
+      </c>
+      <c r="AP26" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP23,"t")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
@@ -5213,7 +5854,6 @@
         <f aca="false">SUM(X24:X26)</f>
         <v>17</v>
       </c>
-      <c r="Y27" s="1"/>
       <c r="Z27" s="1" t="n">
         <f aca="false">SUM(Z24:Z26)</f>
         <v>19</v>
@@ -5233,6 +5873,37 @@
       <c r="AF27" s="1" t="n">
         <f aca="false">SUM(AF24:AF26)</f>
         <v>2</v>
+      </c>
+      <c r="AG27" s="1" t="n">
+        <f aca="false">SUM(AG24:AG26)</f>
+        <v>16</v>
+      </c>
+      <c r="AH27" s="1"/>
+      <c r="AI27" s="1" t="n">
+        <f aca="false">SUM(AI24:AI26)</f>
+        <v>18</v>
+      </c>
+      <c r="AJ27" s="1"/>
+      <c r="AK27" s="1" t="n">
+        <f aca="false">SUM(AK24:AK26)</f>
+        <v>16</v>
+      </c>
+      <c r="AL27" s="1"/>
+      <c r="AM27" s="1" t="n">
+        <f aca="false">SUM(AM24:AM26)</f>
+        <v>15</v>
+      </c>
+      <c r="AN27" s="1" t="n">
+        <f aca="false">SUM(AN24:AN26)</f>
+        <v>16</v>
+      </c>
+      <c r="AO27" s="1" t="n">
+        <f aca="false">SUM(AO24:AO26)</f>
+        <v>13</v>
+      </c>
+      <c r="AP27" s="1" t="n">
+        <f aca="false">SUM(AP24:AP26)</f>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -5706,9 +6377,12 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.94"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="10.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.55"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="6" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="4" min="3" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="12.55"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="19" min="6" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="20" style="1" width="17.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="37.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="12.8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5772,6 +6446,24 @@
       <c r="T1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y1" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z1" s="0" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
@@ -5833,6 +6525,12 @@
         <f aca="false">IF(R2&gt;6,"TEA",IF(R2&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U2" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -5892,6 +6590,12 @@
         <f aca="false">IF(R3&gt;6,"TEA",IF(R3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V3" s="1" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -5952,6 +6656,12 @@
       <c r="S4" s="5" t="str">
         <f aca="false">IF(R4&gt;6,"TEA",IF(R4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6006,6 +6716,15 @@
         <f aca="false">IF(R5&gt;6,"TEA",IF(R5&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -6061,12 +6780,18 @@
         <f aca="false">IF(R6&gt;6,"TEA",IF(R6&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="10" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="2" t="n">
@@ -6114,6 +6839,12 @@
         <f aca="false">IF(R7&gt;6,"TEA",IF(R7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="1" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -6175,6 +6906,12 @@
         <f aca="false">IF(R8&gt;6,"TEA",IF(R8&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -6228,6 +6965,15 @@
         <f aca="false">IF(R9&gt;6,"TEA",IF(R9&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -6283,6 +7029,12 @@
         <f aca="false">IF(R10&gt;6,"TEA",IF(R10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -6342,8 +7094,14 @@
         <f aca="false">IF(R11&gt;6,"TEA",IF(R11&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
@@ -6395,6 +7153,15 @@
         <f aca="false">IF(R12&gt;6,"TEA",IF(R12&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="W12" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -6448,6 +7215,15 @@
         <f aca="false">IF(R13&gt;6,"TEA",IF(R13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -6503,6 +7279,12 @@
         <f aca="false">IF(R14&gt;6,"TEA",IF(R14&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
+      <c r="U14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -6562,6 +7344,15 @@
         <f aca="false">IF(R15&gt;6,"TEA",IF(R15&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
@@ -6623,6 +7414,15 @@
         <f aca="false">IF(R16&gt;6,"TEA",IF(R16&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V16" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="17" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
@@ -6656,7 +7456,7 @@
       <c r="M17" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="N17" s="10" t="n">
+      <c r="N17" s="12" t="n">
         <f aca="false">ROUND(AVERAGE(C17,E17,H17,J17,L17,M17),0)</f>
         <v>3</v>
       </c>
@@ -6678,6 +7478,12 @@
         <f aca="false">IF(R17&gt;6,"TEA",IF(R17&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
+      <c r="U17" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="XFD17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6732,6 +7538,12 @@
         <f aca="false">IF(R18&gt;6,"TEA",IF(R18&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
@@ -6793,6 +7605,12 @@
         <f aca="false">IF(R19&gt;6,"TEA",IF(R19&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
@@ -6854,6 +7672,12 @@
         <f aca="false">IF(R20&gt;6,"TEA",IF(R20&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="U20" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -6913,68 +7737,80 @@
         <f aca="false">IF(R21&gt;6,"TEA",IF(R21&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-    </row>
-    <row r="22" s="12" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="n">
+      <c r="U21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="15" t="n">
         <v>46126</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F22" s="15" t="n">
         <v>46126</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="H22" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="I22" s="13" t="n">
+      <c r="I22" s="15" t="n">
         <v>46126</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="J22" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="K22" s="13" t="n">
+      <c r="K22" s="15" t="n">
         <v>46126</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="L22" s="14" t="n">
         <v>9.33</v>
       </c>
-      <c r="M22" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="N22" s="14" t="n">
+      <c r="M22" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N22" s="16" t="n">
         <f aca="false">ROUND(AVERAGE(C22,E22,H22,J22,L22,M22),0)</f>
         <v>8</v>
       </c>
-      <c r="O22" s="14" t="str">
+      <c r="O22" s="16" t="str">
         <f aca="false">IF(N22&gt;6,"TEA",IF(N22&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="P22" s="11" t="n">
+      <c r="P22" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="Q22" s="12" t="n">
+      <c r="Q22" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="R22" s="14" t="n">
+      <c r="R22" s="16" t="n">
         <f aca="false">ROUND(AVERAGE(N22,Q22),0)</f>
         <v>8</v>
       </c>
-      <c r="S22" s="14" t="str">
+      <c r="S22" s="16" t="str">
         <f aca="false">IF(R22&gt;6,"TEA",IF(R22&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="T22" s="12" t="s">
-        <v>52</v>
+      <c r="T22" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="U22" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V22" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7035,6 +7871,18 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="V2:V22">
+    <cfRule type="cellIs" priority="17" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>4</formula>
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7069,16 +7917,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7486,7 +8334,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7783,16 +8631,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8187,7 +9035,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F29" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G29" s="1" t="n">
         <f aca="false">COUNTIF(G2:G28,"&gt;0")</f>
@@ -8229,16 +9077,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8624,7 +9472,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8920,7 +9768,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
